--- a/research/traditional_assets/database/data/israel/israel_software_internet.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_software_internet.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.36</v>
+        <v>0.284</v>
       </c>
       <c r="G2">
-        <v>0.1781336819741788</v>
+        <v>0.1255490483162518</v>
       </c>
       <c r="H2">
-        <v>-0.147246282072234</v>
+        <v>-0.2245241581259151</v>
       </c>
       <c r="I2">
-        <v>-0.2284364685494338</v>
+        <v>-0.2501739351367985</v>
       </c>
       <c r="J2">
-        <v>-0.1142182342747169</v>
+        <v>-0.2501739351367985</v>
       </c>
       <c r="K2">
-        <v>-17.6</v>
+        <v>-494.9</v>
       </c>
       <c r="L2">
-        <v>-0.01438143487497957</v>
+        <v>-0.362298682284041</v>
       </c>
       <c r="M2">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.02225461505079616</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-11.36363636363636</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +627,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>200</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>287.2</v>
+        <v>299.9</v>
       </c>
       <c r="V2">
-        <v>0.03195762721294328</v>
+        <v>0.06639950405172031</v>
       </c>
       <c r="W2">
-        <v>-0.0657943925233645</v>
+        <v>-2.527579162410623</v>
       </c>
       <c r="X2">
-        <v>0.07171457077099687</v>
+        <v>0.1449713422708075</v>
       </c>
       <c r="Y2">
-        <v>-0.1375089632943614</v>
+        <v>-2.672550504681431</v>
       </c>
       <c r="Z2">
-        <v>1.184701588404621</v>
+        <v>1.455532764936852</v>
       </c>
       <c r="AA2">
-        <v>-0.1353145235700283</v>
+        <v>-0.364136359524797</v>
       </c>
       <c r="AB2">
-        <v>0.06706328138535884</v>
+        <v>0.1270767671582114</v>
       </c>
       <c r="AC2">
-        <v>-0.2023778049553871</v>
+        <v>-0.4912131266830084</v>
       </c>
       <c r="AD2">
-        <v>921.7</v>
+        <v>926.9</v>
       </c>
       <c r="AE2">
-        <v>99.80275105398499</v>
+        <v>108.1879769843339</v>
       </c>
       <c r="AF2">
-        <v>1021.502751053985</v>
+        <v>1035.087976984334</v>
       </c>
       <c r="AG2">
-        <v>734.302751053985</v>
+        <v>735.1879769843339</v>
       </c>
       <c r="AH2">
-        <v>0.1020645128361177</v>
+        <v>0.1864456326211963</v>
       </c>
       <c r="AI2">
-        <v>0.8391525856402862</v>
+        <v>1.066344697294051</v>
       </c>
       <c r="AJ2">
-        <v>0.07553620368368215</v>
+        <v>0.1399881297962244</v>
       </c>
       <c r="AK2">
-        <v>0.7894856242731021</v>
+        <v>1.096006491185968</v>
       </c>
       <c r="AL2">
-        <v>20.5</v>
+        <v>453.9</v>
       </c>
       <c r="AM2">
-        <v>-284.7</v>
+        <v>453.9</v>
       </c>
       <c r="AN2">
-        <v>-3.835622138992925</v>
+        <v>-3.089666666666667</v>
       </c>
       <c r="AO2">
-        <v>-13.79512195121951</v>
+        <v>-0.7695527649261953</v>
       </c>
       <c r="AP2">
-        <v>-3.055775077211756</v>
+        <v>-2.45062658994778</v>
       </c>
       <c r="AQ2">
-        <v>0.9933263083948016</v>
+        <v>-0.7695527649261953</v>
       </c>
     </row>
     <row r="3">
@@ -719,34 +716,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.36</v>
+        <v>0.284</v>
       </c>
       <c r="G3">
-        <v>0.1781336819741788</v>
+        <v>0.1255490483162518</v>
       </c>
       <c r="H3">
-        <v>-0.147246282072234</v>
+        <v>-0.2245241581259151</v>
       </c>
       <c r="I3">
-        <v>-0.2284364685494338</v>
+        <v>-0.2501739351367985</v>
       </c>
       <c r="J3">
-        <v>-0.1142182342747169</v>
+        <v>-0.2501739351367985</v>
       </c>
       <c r="K3">
-        <v>-17.6</v>
+        <v>-494.9</v>
       </c>
       <c r="L3">
-        <v>-0.01438143487497957</v>
+        <v>-0.362298682284041</v>
       </c>
       <c r="M3">
-        <v>200</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.02225461505079616</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-11.36363636363636</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +755,76 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>200</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>287.2</v>
+        <v>299.9</v>
       </c>
       <c r="V3">
-        <v>0.03195762721294328</v>
+        <v>0.06639950405172031</v>
       </c>
       <c r="W3">
-        <v>-0.0657943925233645</v>
+        <v>-2.527579162410623</v>
       </c>
       <c r="X3">
-        <v>0.07171457077099687</v>
+        <v>0.1449713422708075</v>
       </c>
       <c r="Y3">
-        <v>-0.1375089632943614</v>
+        <v>-2.672550504681431</v>
       </c>
       <c r="Z3">
-        <v>1.184701588404621</v>
+        <v>1.455532764936852</v>
       </c>
       <c r="AA3">
-        <v>-0.1353145235700283</v>
+        <v>-0.364136359524797</v>
       </c>
       <c r="AB3">
-        <v>0.06706328138535884</v>
+        <v>0.1270767671582114</v>
       </c>
       <c r="AC3">
-        <v>-0.2023778049553871</v>
+        <v>-0.4912131266830084</v>
       </c>
       <c r="AD3">
-        <v>921.7</v>
+        <v>926.9</v>
       </c>
       <c r="AE3">
-        <v>99.80275105398499</v>
+        <v>108.1879769843339</v>
       </c>
       <c r="AF3">
-        <v>1021.502751053985</v>
+        <v>1035.087976984334</v>
       </c>
       <c r="AG3">
-        <v>734.302751053985</v>
+        <v>735.1879769843339</v>
       </c>
       <c r="AH3">
-        <v>0.1020645128361177</v>
+        <v>0.1864456326211963</v>
       </c>
       <c r="AI3">
-        <v>0.8391525856402862</v>
+        <v>1.066344697294051</v>
       </c>
       <c r="AJ3">
-        <v>0.07553620368368215</v>
+        <v>0.1399881297962244</v>
       </c>
       <c r="AK3">
-        <v>0.7894856242731021</v>
+        <v>1.096006491185968</v>
       </c>
       <c r="AL3">
-        <v>20.5</v>
+        <v>453.9</v>
       </c>
       <c r="AM3">
-        <v>-284.7</v>
+        <v>453.9</v>
       </c>
       <c r="AN3">
-        <v>-3.835622138992925</v>
+        <v>-3.089666666666667</v>
       </c>
       <c r="AO3">
-        <v>-13.79512195121951</v>
+        <v>-0.7695527649261953</v>
       </c>
       <c r="AP3">
-        <v>-3.055775077211756</v>
+        <v>-2.45062658994778</v>
       </c>
       <c r="AQ3">
-        <v>0.9933263083948016</v>
+        <v>-0.7695527649261953</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/israel/israel_software_internet.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_software_internet.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.284</v>
+        <v>0.221</v>
       </c>
       <c r="G2">
-        <v>0.1255490483162518</v>
+        <v>0.1414501949897548</v>
       </c>
       <c r="H2">
-        <v>-0.2245241581259151</v>
+        <v>-0.173507832639302</v>
       </c>
       <c r="I2">
-        <v>-0.2501739351367985</v>
+        <v>-0.03002254218553676</v>
       </c>
       <c r="J2">
-        <v>-0.2501739351367985</v>
+        <v>-0.03002254218553676</v>
       </c>
       <c r="K2">
-        <v>-494.9</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L2">
-        <v>-0.362298682284041</v>
+        <v>-0.005810033710093198</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>300.2</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.0426905574516496</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-34.15244596131969</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,76 +627,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
+        <v>300.2</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>504.8</v>
+      </c>
+      <c r="V2">
+        <v>0.07178612059158135</v>
+      </c>
+      <c r="W2">
+        <v>0.1364906832298136</v>
+      </c>
+      <c r="X2">
+        <v>0.1163571376148812</v>
+      </c>
+      <c r="Y2">
+        <v>0.02013354561493245</v>
+      </c>
+      <c r="Z2">
+        <v>1.880066635206491</v>
+      </c>
+      <c r="AA2">
+        <v>-0.05644437986710701</v>
+      </c>
+      <c r="AB2">
+        <v>0.1089861104374671</v>
+      </c>
+      <c r="AC2">
+        <v>-0.1654304903045741</v>
+      </c>
+      <c r="AD2">
+        <v>568.9</v>
+      </c>
+      <c r="AE2">
+        <v>242.1055203624928</v>
+      </c>
+      <c r="AF2">
+        <v>811.0055203624928</v>
+      </c>
+      <c r="AG2">
+        <v>306.2055203624928</v>
+      </c>
+      <c r="AH2">
+        <v>0.1034049406515029</v>
+      </c>
+      <c r="AI2">
+        <v>1.132206156881321</v>
+      </c>
+      <c r="AJ2">
+        <v>0.0417275748836436</v>
+      </c>
+      <c r="AK2">
+        <v>1.447742450588035</v>
+      </c>
+      <c r="AL2">
         <v>0</v>
       </c>
-      <c r="U2">
-        <v>299.9</v>
-      </c>
-      <c r="V2">
-        <v>0.06639950405172031</v>
-      </c>
-      <c r="W2">
-        <v>-2.527579162410623</v>
-      </c>
-      <c r="X2">
-        <v>0.1449713422708075</v>
-      </c>
-      <c r="Y2">
-        <v>-2.672550504681431</v>
-      </c>
-      <c r="Z2">
-        <v>1.455532764936852</v>
-      </c>
-      <c r="AA2">
-        <v>-0.364136359524797</v>
-      </c>
-      <c r="AB2">
-        <v>0.1270767671582114</v>
-      </c>
-      <c r="AC2">
-        <v>-0.4912131266830084</v>
-      </c>
-      <c r="AD2">
-        <v>926.9</v>
-      </c>
-      <c r="AE2">
-        <v>108.1879769843339</v>
-      </c>
-      <c r="AF2">
-        <v>1035.087976984334</v>
-      </c>
-      <c r="AG2">
-        <v>735.1879769843339</v>
-      </c>
-      <c r="AH2">
-        <v>0.1864456326211963</v>
-      </c>
-      <c r="AI2">
-        <v>1.066344697294051</v>
-      </c>
-      <c r="AJ2">
-        <v>0.1399881297962244</v>
-      </c>
-      <c r="AK2">
-        <v>1.096006491185968</v>
-      </c>
-      <c r="AL2">
-        <v>453.9</v>
-      </c>
       <c r="AM2">
-        <v>453.9</v>
+        <v>-240.5</v>
       </c>
       <c r="AN2">
-        <v>-3.089666666666667</v>
-      </c>
-      <c r="AO2">
-        <v>-0.7695527649261953</v>
+        <v>20.31785714285714</v>
       </c>
       <c r="AP2">
-        <v>-2.45062658994778</v>
+        <v>10.9359114415176</v>
       </c>
       <c r="AQ2">
-        <v>-0.7695527649261953</v>
+        <v>0.1214137214137214</v>
       </c>
     </row>
     <row r="3">
@@ -716,34 +716,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.284</v>
+        <v>0.221</v>
       </c>
       <c r="G3">
-        <v>0.1255490483162518</v>
+        <v>0.1414501949897548</v>
       </c>
       <c r="H3">
-        <v>-0.2245241581259151</v>
+        <v>-0.173507832639302</v>
       </c>
       <c r="I3">
-        <v>-0.2501739351367985</v>
+        <v>-0.03002254218553676</v>
       </c>
       <c r="J3">
-        <v>-0.2501739351367985</v>
+        <v>-0.03002254218553676</v>
       </c>
       <c r="K3">
-        <v>-494.9</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L3">
-        <v>-0.362298682284041</v>
+        <v>-0.005810033710093198</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>300.2</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0426905574516496</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-34.15244596131969</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,76 +755,76 @@
         <v>0</v>
       </c>
       <c r="S3">
+        <v>300.2</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
+        <v>504.8</v>
+      </c>
+      <c r="V3">
+        <v>0.07178612059158135</v>
+      </c>
+      <c r="W3">
+        <v>0.1364906832298136</v>
+      </c>
+      <c r="X3">
+        <v>0.1163571376148812</v>
+      </c>
+      <c r="Y3">
+        <v>0.02013354561493245</v>
+      </c>
+      <c r="Z3">
+        <v>1.880066635206491</v>
+      </c>
+      <c r="AA3">
+        <v>-0.05644437986710701</v>
+      </c>
+      <c r="AB3">
+        <v>0.1089861104374671</v>
+      </c>
+      <c r="AC3">
+        <v>-0.1654304903045741</v>
+      </c>
+      <c r="AD3">
+        <v>568.9</v>
+      </c>
+      <c r="AE3">
+        <v>242.1055203624928</v>
+      </c>
+      <c r="AF3">
+        <v>811.0055203624928</v>
+      </c>
+      <c r="AG3">
+        <v>306.2055203624928</v>
+      </c>
+      <c r="AH3">
+        <v>0.1034049406515029</v>
+      </c>
+      <c r="AI3">
+        <v>1.132206156881321</v>
+      </c>
+      <c r="AJ3">
+        <v>0.0417275748836436</v>
+      </c>
+      <c r="AK3">
+        <v>1.447742450588035</v>
+      </c>
+      <c r="AL3">
         <v>0</v>
       </c>
-      <c r="U3">
-        <v>299.9</v>
-      </c>
-      <c r="V3">
-        <v>0.06639950405172031</v>
-      </c>
-      <c r="W3">
-        <v>-2.527579162410623</v>
-      </c>
-      <c r="X3">
-        <v>0.1449713422708075</v>
-      </c>
-      <c r="Y3">
-        <v>-2.672550504681431</v>
-      </c>
-      <c r="Z3">
-        <v>1.455532764936852</v>
-      </c>
-      <c r="AA3">
-        <v>-0.364136359524797</v>
-      </c>
-      <c r="AB3">
-        <v>0.1270767671582114</v>
-      </c>
-      <c r="AC3">
-        <v>-0.4912131266830084</v>
-      </c>
-      <c r="AD3">
-        <v>926.9</v>
-      </c>
-      <c r="AE3">
-        <v>108.1879769843339</v>
-      </c>
-      <c r="AF3">
-        <v>1035.087976984334</v>
-      </c>
-      <c r="AG3">
-        <v>735.1879769843339</v>
-      </c>
-      <c r="AH3">
-        <v>0.1864456326211963</v>
-      </c>
-      <c r="AI3">
-        <v>1.066344697294051</v>
-      </c>
-      <c r="AJ3">
-        <v>0.1399881297962244</v>
-      </c>
-      <c r="AK3">
-        <v>1.096006491185968</v>
-      </c>
-      <c r="AL3">
-        <v>453.9</v>
-      </c>
       <c r="AM3">
-        <v>453.9</v>
+        <v>-240.5</v>
       </c>
       <c r="AN3">
-        <v>-3.089666666666667</v>
-      </c>
-      <c r="AO3">
-        <v>-0.7695527649261953</v>
+        <v>20.31785714285714</v>
       </c>
       <c r="AP3">
-        <v>-2.45062658994778</v>
+        <v>10.9359114415176</v>
       </c>
       <c r="AQ3">
-        <v>-0.7695527649261953</v>
+        <v>0.1214137214137214</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/israel/israel_software_internet.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_software_internet.xlsx
@@ -1269,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1406,22 +1406,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1275669197969841</v>
+        <v>0.127308165881451</v>
       </c>
       <c r="C2">
-        <v>12920.71868103251</v>
+        <v>12829.93528735021</v>
       </c>
       <c r="D2">
-        <v>12481.31868103251</v>
+        <v>12520.94158316517</v>
       </c>
       <c r="E2">
-        <v>-1031.629581495622</v>
+        <v>-901.2232856806658</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>130.4062958149562</v>
       </c>
       <c r="G2">
         <v>439.4</v>
@@ -1442,28 +1442,28 @@
         <v>92.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>6.559436679492298</v>
       </c>
       <c r="N2">
-        <v>92.3</v>
+        <v>85.7405633205077</v>
       </c>
       <c r="O2">
-        <v>21.229</v>
+        <v>19.72032956371677</v>
       </c>
       <c r="P2">
-        <v>71.071</v>
+        <v>66.02023375679093</v>
       </c>
       <c r="Q2">
-        <v>102.671</v>
+        <v>97.62023375679094</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1275669197969841</v>
+        <v>0.1282028847287384</v>
       </c>
       <c r="T2">
-        <v>1.264908244262672</v>
+        <v>1.274746419495827</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>14.07133028489636</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1488,22 +1488,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.127308165881451</v>
+        <v>0.1270725119659179</v>
       </c>
       <c r="C3">
-        <v>12829.93528735021</v>
+        <v>12735.83411904837</v>
       </c>
       <c r="D3">
-        <v>12520.94158316517</v>
+        <v>12557.24671067828</v>
       </c>
       <c r="E3">
-        <v>-901.2232856806658</v>
+        <v>-770.8169898657095</v>
       </c>
       <c r="F3">
-        <v>130.4062958149562</v>
+        <v>260.8125916299124</v>
       </c>
       <c r="G3">
         <v>439.4</v>
@@ -1524,45 +1524,45 @@
         <v>92.3</v>
       </c>
       <c r="M3">
-        <v>6.559436679492298</v>
+        <v>13.51009224642946</v>
       </c>
       <c r="N3">
-        <v>85.7405633205077</v>
+        <v>78.78990775357053</v>
       </c>
       <c r="O3">
-        <v>19.72032956371677</v>
+        <v>18.12167878332122</v>
       </c>
       <c r="P3">
-        <v>66.02023375679093</v>
+        <v>60.66822897024931</v>
       </c>
       <c r="Q3">
-        <v>97.62023375679094</v>
+        <v>92.26822897024931</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1282028847287384</v>
+        <v>0.1288518285366509</v>
       </c>
       <c r="T3">
-        <v>1.274746419495827</v>
+        <v>1.284785373815372</v>
       </c>
       <c r="U3">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V3">
         <v>0.23</v>
       </c>
       <c r="W3">
-        <v>0.038731</v>
+        <v>0.039886</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y3">
-        <v>14.07133028489636</v>
+        <v>6.831929665350261</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1570,22 +1570,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1270725119659179</v>
+        <v>0.1268830580503849</v>
       </c>
       <c r="C4">
-        <v>12735.83411904837</v>
+        <v>12634.76834904553</v>
       </c>
       <c r="D4">
-        <v>12557.24671067828</v>
+        <v>12586.5872364904</v>
       </c>
       <c r="E4">
-        <v>-770.8169898657095</v>
+        <v>-640.4106940507534</v>
       </c>
       <c r="F4">
-        <v>260.8125916299124</v>
+        <v>391.2188874448686</v>
       </c>
       <c r="G4">
         <v>439.4</v>
@@ -1606,45 +1606,45 @@
         <v>92.3</v>
       </c>
       <c r="M4">
-        <v>13.51009224642946</v>
+        <v>21.24318558825637</v>
       </c>
       <c r="N4">
-        <v>78.78990775357053</v>
+        <v>71.05681441174363</v>
       </c>
       <c r="O4">
-        <v>18.12167878332122</v>
+        <v>16.34306731470103</v>
       </c>
       <c r="P4">
-        <v>60.66822897024931</v>
+        <v>54.7137470970426</v>
       </c>
       <c r="Q4">
-        <v>92.26822897024931</v>
+        <v>86.31374709704261</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1288518285366509</v>
+        <v>0.1295141526292627</v>
       </c>
       <c r="T4">
-        <v>1.284785373815372</v>
+        <v>1.295031316883773</v>
       </c>
       <c r="U4">
-        <v>0.0518</v>
+        <v>0.0543</v>
       </c>
       <c r="V4">
         <v>0.23</v>
       </c>
       <c r="W4">
-        <v>0.039886</v>
+        <v>0.041811</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y4">
-        <v>6.831929665350261</v>
+        <v>4.344922733764807</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1652,22 +1652,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1268830580503849</v>
+        <v>0.1266859041348518</v>
       </c>
       <c r="C5">
-        <v>12634.76834904553</v>
+        <v>12535.04100753558</v>
       </c>
       <c r="D5">
-        <v>12586.5872364904</v>
+        <v>12617.26619079541</v>
       </c>
       <c r="E5">
-        <v>-640.4106940507534</v>
+        <v>-510.0043982357971</v>
       </c>
       <c r="F5">
-        <v>391.2188874448686</v>
+        <v>521.6251832598249</v>
       </c>
       <c r="G5">
         <v>439.4</v>
@@ -1688,45 +1688,45 @@
         <v>92.3</v>
       </c>
       <c r="M5">
-        <v>21.24318558825637</v>
+        <v>28.84587263426832</v>
       </c>
       <c r="N5">
-        <v>71.05681441174363</v>
+        <v>63.45412736573168</v>
       </c>
       <c r="O5">
-        <v>16.34306731470103</v>
+        <v>14.59444929411829</v>
       </c>
       <c r="P5">
-        <v>54.7137470970426</v>
+        <v>48.85967807161339</v>
       </c>
       <c r="Q5">
-        <v>86.31374709704261</v>
+        <v>80.45967807161341</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1295141526292627</v>
+        <v>0.1301902751404706</v>
       </c>
       <c r="T5">
-        <v>1.295031316883773</v>
+        <v>1.305490717099433</v>
       </c>
       <c r="U5">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V5">
         <v>0.23</v>
       </c>
       <c r="W5">
-        <v>0.041811</v>
+        <v>0.042581</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y5">
-        <v>4.344922733764807</v>
+        <v>3.199764526809616</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1734,22 +1734,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1266859041348518</v>
+        <v>0.1266966502193187</v>
       </c>
       <c r="C6">
-        <v>12535.04100753558</v>
+        <v>12402.95866941405</v>
       </c>
       <c r="D6">
-        <v>12617.26619079541</v>
+        <v>12615.59014848883</v>
       </c>
       <c r="E6">
-        <v>-510.0043982357971</v>
+        <v>-379.5981024208409</v>
       </c>
       <c r="F6">
-        <v>521.6251832598249</v>
+        <v>652.0314790747811</v>
       </c>
       <c r="G6">
         <v>439.4</v>
@@ -1770,45 +1770,45 @@
         <v>92.3</v>
       </c>
       <c r="M6">
-        <v>28.84587263426832</v>
+        <v>39.96952966728409</v>
       </c>
       <c r="N6">
-        <v>63.45412736573168</v>
+        <v>52.33047033271591</v>
       </c>
       <c r="O6">
-        <v>14.59444929411829</v>
+        <v>12.03600817652466</v>
       </c>
       <c r="P6">
-        <v>48.85967807161339</v>
+        <v>40.29446215619125</v>
       </c>
       <c r="Q6">
-        <v>80.45967807161341</v>
+        <v>71.89446215619125</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1301902751404706</v>
+        <v>0.1308806318098092</v>
       </c>
       <c r="T6">
-        <v>1.305490717099433</v>
+        <v>1.31617031521437</v>
       </c>
       <c r="U6">
-        <v>0.0553</v>
+        <v>0.0613</v>
       </c>
       <c r="V6">
         <v>0.23</v>
       </c>
       <c r="W6">
-        <v>0.042581</v>
+        <v>0.047201</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y6">
-        <v>3.199764526809616</v>
+        <v>2.309259097325569</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1816,22 +1816,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1266966502193187</v>
+        <v>0.1271924963037857</v>
       </c>
       <c r="C7">
-        <v>12402.95866941405</v>
+        <v>12195.69773389102</v>
       </c>
       <c r="D7">
-        <v>12615.59014848883</v>
+        <v>12538.73550878076</v>
       </c>
       <c r="E7">
-        <v>-379.5981024208409</v>
+        <v>-249.1918066058847</v>
       </c>
       <c r="F7">
-        <v>652.0314790747811</v>
+        <v>782.4377748897373</v>
       </c>
       <c r="G7">
         <v>439.4</v>
@@ -1852,45 +1852,45 @@
         <v>92.3</v>
       </c>
       <c r="M7">
-        <v>39.96952966728409</v>
+        <v>59.30878333664209</v>
       </c>
       <c r="N7">
-        <v>52.33047033271591</v>
+        <v>32.9912166633579</v>
       </c>
       <c r="O7">
-        <v>12.03600817652466</v>
+        <v>7.587979832572318</v>
       </c>
       <c r="P7">
-        <v>40.29446215619125</v>
+        <v>25.40323683078558</v>
       </c>
       <c r="Q7">
-        <v>71.89446215619125</v>
+        <v>57.0032368307856</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1308806318098092</v>
+        <v>0.131585676918921</v>
       </c>
       <c r="T7">
-        <v>1.31617031521437</v>
+        <v>1.327077138821115</v>
       </c>
       <c r="U7">
-        <v>0.0613</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V7">
         <v>0.23</v>
       </c>
       <c r="W7">
-        <v>0.047201</v>
+        <v>0.05836600000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y7">
-        <v>2.309259097325569</v>
+        <v>1.556261902661141</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1898,22 +1898,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1271924963037857</v>
+        <v>0.1299126689256004</v>
       </c>
       <c r="C8">
-        <v>12195.69773389102</v>
+        <v>11659.79336651528</v>
       </c>
       <c r="D8">
-        <v>12538.73550878076</v>
+        <v>12133.23743721998</v>
       </c>
       <c r="E8">
-        <v>-249.1918066058847</v>
+        <v>-118.7855107909286</v>
       </c>
       <c r="F8">
-        <v>782.4377748897373</v>
+        <v>912.8440707046934</v>
       </c>
       <c r="G8">
         <v>439.4</v>
@@ -1934,45 +1934,45 @@
         <v>92.3</v>
       </c>
       <c r="M8">
-        <v>59.30878333664209</v>
+        <v>108.2633067855766</v>
       </c>
       <c r="N8">
-        <v>32.9912166633579</v>
+        <v>-15.96330678557665</v>
       </c>
       <c r="O8">
-        <v>7.587979832572318</v>
+        <v>-3.671560560682629</v>
       </c>
       <c r="P8">
-        <v>25.40323683078558</v>
+        <v>-12.29174622489402</v>
       </c>
       <c r="Q8">
-        <v>57.0032368307856</v>
+        <v>19.30825377510599</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1315856769189209</v>
+        <v>0.1325146033615699</v>
       </c>
       <c r="T8">
-        <v>1.327077138821114</v>
+        <v>1.341447335454884</v>
       </c>
       <c r="U8">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V8">
-        <v>0.23</v>
+        <v>0.1960867502601374</v>
       </c>
       <c r="W8">
-        <v>0.05836600000000001</v>
+        <v>0.09534411141914773</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y8">
-        <v>1.556261902661141</v>
+        <v>0.8525510880875536</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1980,22 +1980,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1299126689256004</v>
+        <v>0.137676112345588</v>
       </c>
       <c r="C9">
-        <v>11659.79336651529</v>
+        <v>10504.14013827877</v>
       </c>
       <c r="D9">
-        <v>12133.23743721998</v>
+        <v>11107.99050479842</v>
       </c>
       <c r="E9">
-        <v>-118.7855107909285</v>
+        <v>11.62078502402778</v>
       </c>
       <c r="F9">
-        <v>912.8440707046935</v>
+        <v>1043.25036651965</v>
       </c>
       <c r="G9">
         <v>439.4</v>
@@ -2016,45 +2016,45 @@
         <v>92.3</v>
       </c>
       <c r="M9">
-        <v>108.2633067855767</v>
+        <v>209.4846735971457</v>
       </c>
       <c r="N9">
-        <v>-15.96330678557666</v>
+        <v>-117.1846735971457</v>
       </c>
       <c r="O9">
-        <v>-3.671560560682633</v>
+        <v>-26.95247492734351</v>
       </c>
       <c r="P9">
-        <v>-12.29174622489403</v>
+        <v>-90.23219866980217</v>
       </c>
       <c r="Q9">
-        <v>19.30825377510598</v>
+        <v>-58.63219866980216</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1325146033615699</v>
+        <v>0.1339565484198344</v>
       </c>
       <c r="T9">
-        <v>1.341447335454884</v>
+        <v>1.363753766912754</v>
       </c>
       <c r="U9">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V9">
-        <v>0.1960867502601373</v>
+        <v>0.1013391559175585</v>
       </c>
       <c r="W9">
-        <v>0.09534411141914773</v>
+        <v>0.1804510974917543</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y9">
-        <v>0.8525510880875535</v>
+        <v>0.4406050257285153</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2062,22 +2062,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.137676112345588</v>
+        <v>0.139226112345588</v>
       </c>
       <c r="C10">
-        <v>10504.14013827877</v>
+        <v>10189.44505156614</v>
       </c>
       <c r="D10">
-        <v>11107.99050479842</v>
+        <v>10923.70171390075</v>
       </c>
       <c r="E10">
-        <v>11.62078502402778</v>
+        <v>142.0270808389839</v>
       </c>
       <c r="F10">
-        <v>1043.25036651965</v>
+        <v>1173.656662334606</v>
       </c>
       <c r="G10">
         <v>439.4</v>
@@ -2098,37 +2098,37 @@
         <v>92.3</v>
       </c>
       <c r="M10">
-        <v>209.4846735971457</v>
+        <v>235.6702577967889</v>
       </c>
       <c r="N10">
-        <v>-117.1846735971457</v>
+        <v>-143.3702577967889</v>
       </c>
       <c r="O10">
-        <v>-26.95247492734351</v>
+        <v>-32.97515929326145</v>
       </c>
       <c r="P10">
-        <v>-90.23219866980217</v>
+        <v>-110.3950985035275</v>
       </c>
       <c r="Q10">
-        <v>-58.63219866980216</v>
+        <v>-78.79509850352746</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1339565484198344</v>
+        <v>0.1349253016991732</v>
       </c>
       <c r="T10">
-        <v>1.363753766912754</v>
+        <v>1.378740072043663</v>
       </c>
       <c r="U10">
         <v>0.2008</v>
       </c>
       <c r="V10">
-        <v>0.1013391559175585</v>
+        <v>0.09007924970449646</v>
       </c>
       <c r="W10">
-        <v>0.1804510974917543</v>
+        <v>0.1827120866593371</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>0.4406050257285153</v>
+        <v>0.3916489117586802</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2144,22 +2144,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.139226112345588</v>
+        <v>0.140776112345588</v>
       </c>
       <c r="C11">
-        <v>10189.44505156614</v>
+        <v>9880.765111585415</v>
       </c>
       <c r="D11">
-        <v>10923.70171390075</v>
+        <v>10745.42806973498</v>
       </c>
       <c r="E11">
-        <v>142.0270808389839</v>
+        <v>272.4333766539401</v>
       </c>
       <c r="F11">
-        <v>1173.656662334606</v>
+        <v>1304.062958149562</v>
       </c>
       <c r="G11">
         <v>439.4</v>
@@ -2180,37 +2180,37 @@
         <v>92.3</v>
       </c>
       <c r="M11">
-        <v>235.6702577967889</v>
+        <v>261.855841996432</v>
       </c>
       <c r="N11">
-        <v>-143.3702577967889</v>
+        <v>-169.555841996432</v>
       </c>
       <c r="O11">
-        <v>-32.97515929326145</v>
+        <v>-38.99784365917937</v>
       </c>
       <c r="P11">
-        <v>-110.3950985035275</v>
+        <v>-130.5579983372527</v>
       </c>
       <c r="Q11">
-        <v>-78.79509850352746</v>
+        <v>-98.95799833725268</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1349253016991732</v>
+        <v>0.135915582829164</v>
       </c>
       <c r="T11">
-        <v>1.378740072043663</v>
+        <v>1.394059406177481</v>
       </c>
       <c r="U11">
         <v>0.2008</v>
       </c>
       <c r="V11">
-        <v>0.09007924970449646</v>
+        <v>0.08107132473404684</v>
       </c>
       <c r="W11">
-        <v>0.1827120866593371</v>
+        <v>0.1845208779934034</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>0.3916489117586802</v>
+        <v>0.3524840205828124</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2226,22 +2226,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.140776112345588</v>
+        <v>0.142326112345588</v>
       </c>
       <c r="C12">
-        <v>9880.765111585413</v>
+        <v>9577.810547707422</v>
       </c>
       <c r="D12">
-        <v>10745.42806973498</v>
+        <v>10572.87980167194</v>
       </c>
       <c r="E12">
-        <v>272.4333766539403</v>
+        <v>402.8396724688964</v>
       </c>
       <c r="F12">
-        <v>1304.062958149562</v>
+        <v>1434.469253964518</v>
       </c>
       <c r="G12">
         <v>439.4</v>
@@ -2262,37 +2262,37 @@
         <v>92.3</v>
       </c>
       <c r="M12">
-        <v>261.8558419964321</v>
+        <v>288.0414261960753</v>
       </c>
       <c r="N12">
-        <v>-169.5558419964321</v>
+        <v>-195.7414261960753</v>
       </c>
       <c r="O12">
-        <v>-38.99784365917938</v>
+        <v>-45.02052802509731</v>
       </c>
       <c r="P12">
-        <v>-130.5579983372527</v>
+        <v>-150.720898170978</v>
       </c>
       <c r="Q12">
-        <v>-98.9579983372527</v>
+        <v>-119.120898170978</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.135915582829164</v>
+        <v>0.136928117467694</v>
       </c>
       <c r="T12">
-        <v>1.394059406177481</v>
+        <v>1.409722995010936</v>
       </c>
       <c r="U12">
         <v>0.2008</v>
       </c>
       <c r="V12">
-        <v>0.08107132473404681</v>
+        <v>0.07370120430367894</v>
       </c>
       <c r="W12">
-        <v>0.1845208779934034</v>
+        <v>0.1860007981758213</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.3524840205828123</v>
+        <v>0.3204400187116475</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2308,22 +2308,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.142326112345588</v>
+        <v>0.143876112345588</v>
       </c>
       <c r="C13">
-        <v>9577.810547707422</v>
+        <v>9280.309907503633</v>
       </c>
       <c r="D13">
-        <v>10572.87980167194</v>
+        <v>10405.78545728311</v>
       </c>
       <c r="E13">
-        <v>402.8396724688964</v>
+        <v>533.2459682838526</v>
       </c>
       <c r="F13">
-        <v>1434.469253964518</v>
+        <v>1564.875549779475</v>
       </c>
       <c r="G13">
         <v>439.4</v>
@@ -2344,37 +2344,37 @@
         <v>92.3</v>
       </c>
       <c r="M13">
-        <v>288.0414261960753</v>
+        <v>314.2270103957185</v>
       </c>
       <c r="N13">
-        <v>-195.7414261960753</v>
+        <v>-221.9270103957185</v>
       </c>
       <c r="O13">
-        <v>-45.02052802509731</v>
+        <v>-51.04321239101525</v>
       </c>
       <c r="P13">
-        <v>-150.720898170978</v>
+        <v>-170.8837980047032</v>
       </c>
       <c r="Q13">
-        <v>-119.120898170978</v>
+        <v>-139.2837980047032</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.136928117467694</v>
+        <v>0.1379636642570996</v>
       </c>
       <c r="T13">
-        <v>1.409722995010936</v>
+        <v>1.425742574499697</v>
       </c>
       <c r="U13">
         <v>0.2008</v>
       </c>
       <c r="V13">
-        <v>0.07370120430367894</v>
+        <v>0.06755943727837235</v>
       </c>
       <c r="W13">
-        <v>0.1860007981758213</v>
+        <v>0.1872340649945028</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.3204400187116475</v>
+        <v>0.2937366838190103</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2390,22 +2390,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.143876112345588</v>
+        <v>0.145426112345588</v>
       </c>
       <c r="C14">
-        <v>9280.309907503633</v>
+        <v>8988.008631757715</v>
       </c>
       <c r="D14">
-        <v>10405.78545728311</v>
+        <v>10243.89047735215</v>
       </c>
       <c r="E14">
-        <v>533.2459682838526</v>
+        <v>663.6522640988087</v>
       </c>
       <c r="F14">
-        <v>1564.875549779475</v>
+        <v>1695.281845594431</v>
       </c>
       <c r="G14">
         <v>439.4</v>
@@ -2426,37 +2426,37 @@
         <v>92.3</v>
       </c>
       <c r="M14">
-        <v>314.2270103957185</v>
+        <v>340.4125945953617</v>
       </c>
       <c r="N14">
-        <v>-221.9270103957185</v>
+        <v>-248.1125945953617</v>
       </c>
       <c r="O14">
-        <v>-51.04321239101525</v>
+        <v>-57.0658967569332</v>
       </c>
       <c r="P14">
-        <v>-170.8837980047032</v>
+        <v>-191.0466978384285</v>
       </c>
       <c r="Q14">
-        <v>-139.2837980047032</v>
+        <v>-159.4466978384285</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1379636642570996</v>
+        <v>0.1390230167198249</v>
       </c>
       <c r="T14">
-        <v>1.425742574499697</v>
+        <v>1.442130420183601</v>
       </c>
       <c r="U14">
         <v>0.2008</v>
       </c>
       <c r="V14">
-        <v>0.06755943727837235</v>
+        <v>0.06236255748772832</v>
       </c>
       <c r="W14">
-        <v>0.1872340649945028</v>
+        <v>0.1882775984564642</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.2937366838190103</v>
+        <v>0.271141554294471</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2472,22 +2472,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.145426112345588</v>
+        <v>0.146976112345588</v>
       </c>
       <c r="C15">
-        <v>8988.008631757715</v>
+        <v>8700.667760460545</v>
       </c>
       <c r="D15">
-        <v>10243.89047735215</v>
+        <v>10086.95590186993</v>
       </c>
       <c r="E15">
-        <v>663.6522640988087</v>
+        <v>794.0585599137651</v>
       </c>
       <c r="F15">
-        <v>1695.281845594431</v>
+        <v>1825.688141409387</v>
       </c>
       <c r="G15">
         <v>439.4</v>
@@ -2508,37 +2508,37 @@
         <v>92.3</v>
       </c>
       <c r="M15">
-        <v>340.4125945953617</v>
+        <v>366.5981787950049</v>
       </c>
       <c r="N15">
-        <v>-248.1125945953617</v>
+        <v>-274.2981787950049</v>
       </c>
       <c r="O15">
-        <v>-57.0658967569332</v>
+        <v>-63.08858112285113</v>
       </c>
       <c r="P15">
-        <v>-191.0466978384285</v>
+        <v>-211.2095976721538</v>
       </c>
       <c r="Q15">
-        <v>-159.4466978384285</v>
+        <v>-179.6095976721538</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1390230167198249</v>
+        <v>0.1401070052863345</v>
       </c>
       <c r="T15">
-        <v>1.442130420183601</v>
+        <v>1.458899378557829</v>
       </c>
       <c r="U15">
         <v>0.2008</v>
       </c>
       <c r="V15">
-        <v>0.06236255748772832</v>
+        <v>0.05790808909574773</v>
       </c>
       <c r="W15">
-        <v>0.1882775984564642</v>
+        <v>0.1891720557095738</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.271141554294471</v>
+        <v>0.2517743004162944</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2554,22 +2554,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.146976112345588</v>
+        <v>0.148526112345588</v>
       </c>
       <c r="C16">
-        <v>8700.667760460545</v>
+        <v>8418.062755954068</v>
       </c>
       <c r="D16">
-        <v>10086.95590186993</v>
+        <v>9934.757193178411</v>
       </c>
       <c r="E16">
-        <v>794.0585599137651</v>
+        <v>924.4648557287214</v>
       </c>
       <c r="F16">
-        <v>1825.688141409387</v>
+        <v>1956.094437224343</v>
       </c>
       <c r="G16">
         <v>439.4</v>
@@ -2590,37 +2590,37 @@
         <v>92.3</v>
       </c>
       <c r="M16">
-        <v>366.5981787950049</v>
+        <v>392.7837629946482</v>
       </c>
       <c r="N16">
-        <v>-274.2981787950049</v>
+        <v>-300.4837629946481</v>
       </c>
       <c r="O16">
-        <v>-63.08858112285113</v>
+        <v>-69.11126548876908</v>
       </c>
       <c r="P16">
-        <v>-211.2095976721538</v>
+        <v>-231.3724975058791</v>
       </c>
       <c r="Q16">
-        <v>-179.6095976721538</v>
+        <v>-199.7724975058791</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1401070052863345</v>
+        <v>0.1412164994661737</v>
       </c>
       <c r="T16">
-        <v>1.458899378557829</v>
+        <v>1.47606290065851</v>
       </c>
       <c r="U16">
         <v>0.2008</v>
       </c>
       <c r="V16">
-        <v>0.05790808909574773</v>
+        <v>0.05404754982269788</v>
       </c>
       <c r="W16">
-        <v>0.1891720557095738</v>
+        <v>0.1899472519956023</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.2517743004162944</v>
+        <v>0.2349893470552081</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2636,22 +2636,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.148526112345588</v>
+        <v>0.150076112345588</v>
       </c>
       <c r="C17">
-        <v>8418.062755954068</v>
+        <v>8139.98243103461</v>
       </c>
       <c r="D17">
-        <v>9934.757193178411</v>
+        <v>9787.083164073911</v>
       </c>
       <c r="E17">
-        <v>924.464855728721</v>
+        <v>1054.871151543678</v>
       </c>
       <c r="F17">
-        <v>1956.094437224343</v>
+        <v>2086.5007330393</v>
       </c>
       <c r="G17">
         <v>439.4</v>
@@ -2672,37 +2672,37 @@
         <v>92.3</v>
       </c>
       <c r="M17">
-        <v>392.7837629946481</v>
+        <v>418.9693471942913</v>
       </c>
       <c r="N17">
-        <v>-300.4837629946481</v>
+        <v>-326.6693471942913</v>
       </c>
       <c r="O17">
-        <v>-69.11126548876906</v>
+        <v>-75.133949854687</v>
       </c>
       <c r="P17">
-        <v>-231.372497505879</v>
+        <v>-251.5353973396043</v>
       </c>
       <c r="Q17">
-        <v>-199.772497505879</v>
+        <v>-219.9353973396043</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1412164994661737</v>
+        <v>0.1423524101741044</v>
       </c>
       <c r="T17">
-        <v>1.47606290065851</v>
+        <v>1.493635078047302</v>
       </c>
       <c r="U17">
         <v>0.2008</v>
       </c>
       <c r="V17">
-        <v>0.05404754982269788</v>
+        <v>0.05066957795877926</v>
       </c>
       <c r="W17">
-        <v>0.1899472519956023</v>
+        <v>0.1906255487458771</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.2349893470552082</v>
+        <v>0.2203025128642577</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2718,22 +2718,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.150076112345588</v>
+        <v>0.151626112345588</v>
       </c>
       <c r="C18">
-        <v>8139.98243103461</v>
+        <v>7866.22797125446</v>
       </c>
       <c r="D18">
-        <v>9787.083164073911</v>
+        <v>9643.735000108716</v>
       </c>
       <c r="E18">
-        <v>1054.871151543678</v>
+        <v>1185.277447358634</v>
       </c>
       <c r="F18">
-        <v>2086.5007330393</v>
+        <v>2216.907028854256</v>
       </c>
       <c r="G18">
         <v>439.4</v>
@@ -2754,37 +2754,37 @@
         <v>92.3</v>
       </c>
       <c r="M18">
-        <v>418.9693471942913</v>
+        <v>445.1549313939346</v>
       </c>
       <c r="N18">
-        <v>-326.6693471942913</v>
+        <v>-352.8549313939346</v>
       </c>
       <c r="O18">
-        <v>-75.133949854687</v>
+        <v>-81.15663422060496</v>
       </c>
       <c r="P18">
-        <v>-251.5353973396043</v>
+        <v>-271.6982971733296</v>
       </c>
       <c r="Q18">
-        <v>-219.9353973396043</v>
+        <v>-240.0982971733296</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1423524101741044</v>
+        <v>0.1435156922243948</v>
       </c>
       <c r="T18">
-        <v>1.493635078047302</v>
+        <v>1.511630681397269</v>
       </c>
       <c r="U18">
         <v>0.2008</v>
       </c>
       <c r="V18">
-        <v>0.05066957795877926</v>
+        <v>0.0476890145494393</v>
       </c>
       <c r="W18">
-        <v>0.1906255487458771</v>
+        <v>0.1912240458784726</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.2203025128642577</v>
+        <v>0.2073435415193013</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2800,22 +2800,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.151626112345588</v>
+        <v>0.1595745064667745</v>
       </c>
       <c r="C19">
-        <v>7866.22797125446</v>
+        <v>7062.10127038963</v>
       </c>
       <c r="D19">
-        <v>9643.735000108716</v>
+        <v>8970.014595058843</v>
       </c>
       <c r="E19">
-        <v>1185.277447358634</v>
+        <v>1315.68374317359</v>
       </c>
       <c r="F19">
-        <v>2216.907028854256</v>
+        <v>2347.313324669212</v>
       </c>
       <c r="G19">
         <v>439.4</v>
@@ -2836,45 +2836,45 @@
         <v>92.3</v>
       </c>
       <c r="M19">
-        <v>445.1549313939346</v>
+        <v>553.4964819570001</v>
       </c>
       <c r="N19">
-        <v>-352.8549313939346</v>
+        <v>-461.1964819570001</v>
       </c>
       <c r="O19">
-        <v>-81.15663422060496</v>
+        <v>-106.07519085011</v>
       </c>
       <c r="P19">
-        <v>-271.6982971733296</v>
+        <v>-355.1212911068901</v>
       </c>
       <c r="Q19">
-        <v>-240.0982971733296</v>
+        <v>-323.5212911068901</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1435156922243948</v>
+        <v>0.1448273398383343</v>
       </c>
       <c r="T19">
-        <v>1.511630681397269</v>
+        <v>1.531921452830985</v>
       </c>
       <c r="U19">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.0476890145494393</v>
+        <v>0.0383543539878348</v>
       </c>
       <c r="W19">
-        <v>0.1912240458784726</v>
+        <v>0.2267560433296686</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y19">
-        <v>0.2073435415193013</v>
+        <v>0.1667580608166731</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2882,22 +2882,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1595745064667745</v>
+        <v>0.1614745064667745</v>
       </c>
       <c r="C20">
-        <v>7062.10127038963</v>
+        <v>6784.358899831994</v>
       </c>
       <c r="D20">
-        <v>8970.014595058843</v>
+        <v>8822.678520316162</v>
       </c>
       <c r="E20">
-        <v>1315.68374317359</v>
+        <v>1446.090038988546</v>
       </c>
       <c r="F20">
-        <v>2347.313324669212</v>
+        <v>2477.719620484168</v>
       </c>
       <c r="G20">
         <v>439.4</v>
@@ -2918,37 +2918,37 @@
         <v>92.3</v>
       </c>
       <c r="M20">
-        <v>553.4964819570001</v>
+        <v>584.2462865101668</v>
       </c>
       <c r="N20">
-        <v>-461.1964819570001</v>
+        <v>-491.9462865101668</v>
       </c>
       <c r="O20">
-        <v>-106.07519085011</v>
+        <v>-113.1476458973384</v>
       </c>
       <c r="P20">
-        <v>-355.1212911068901</v>
+        <v>-378.7986406128284</v>
       </c>
       <c r="Q20">
-        <v>-323.5212911068901</v>
+        <v>-347.1986406128284</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1448273398383343</v>
+        <v>0.1460498995894249</v>
       </c>
       <c r="T20">
-        <v>1.531921452830985</v>
+        <v>1.550834063359763</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.0383543539878348</v>
+        <v>0.03633570377794876</v>
       </c>
       <c r="W20">
-        <v>0.2267560433296686</v>
+        <v>0.2272320410491597</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.1667580608166731</v>
+        <v>0.1579813207736903</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2964,22 +2964,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1614745064667745</v>
+        <v>0.1633745064667745</v>
       </c>
       <c r="C21">
-        <v>6784.358899831994</v>
+        <v>6511.378421123589</v>
       </c>
       <c r="D21">
-        <v>8822.678520316162</v>
+        <v>8680.104337422714</v>
       </c>
       <c r="E21">
-        <v>1446.090038988546</v>
+        <v>1576.496334803503</v>
       </c>
       <c r="F21">
-        <v>2477.719620484168</v>
+        <v>2608.125916299125</v>
       </c>
       <c r="G21">
         <v>439.4</v>
@@ -3000,37 +3000,37 @@
         <v>92.3</v>
       </c>
       <c r="M21">
-        <v>584.2462865101668</v>
+        <v>614.9960910633336</v>
       </c>
       <c r="N21">
-        <v>-491.9462865101668</v>
+        <v>-522.6960910633336</v>
       </c>
       <c r="O21">
-        <v>-113.1476458973384</v>
+        <v>-120.2201009445667</v>
       </c>
       <c r="P21">
-        <v>-378.7986406128284</v>
+        <v>-402.4759901187668</v>
       </c>
       <c r="Q21">
-        <v>-347.1986406128284</v>
+        <v>-370.8759901187668</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1460498995894249</v>
+        <v>0.1473030233342927</v>
       </c>
       <c r="T21">
-        <v>1.550834063359763</v>
+        <v>1.57021948915176</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.03633570377794876</v>
+        <v>0.03451891858905132</v>
       </c>
       <c r="W21">
-        <v>0.2272320410491597</v>
+        <v>0.2276604389967017</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.1579813207736903</v>
+        <v>0.1500822547350057</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3046,22 +3046,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1633745064667745</v>
+        <v>0.1652745064667745</v>
       </c>
       <c r="C22">
-        <v>6511.378421123589</v>
+        <v>6242.932649534027</v>
       </c>
       <c r="D22">
-        <v>8680.104337422714</v>
+        <v>8542.064861648108</v>
       </c>
       <c r="E22">
-        <v>1576.496334803503</v>
+        <v>1706.902630618459</v>
       </c>
       <c r="F22">
-        <v>2608.125916299125</v>
+        <v>2738.532212114081</v>
       </c>
       <c r="G22">
         <v>439.4</v>
@@ -3082,37 +3082,37 @@
         <v>92.3</v>
       </c>
       <c r="M22">
-        <v>614.9960910633336</v>
+        <v>645.7458956165002</v>
       </c>
       <c r="N22">
-        <v>-522.6960910633336</v>
+        <v>-553.4458956165003</v>
       </c>
       <c r="O22">
-        <v>-120.2201009445667</v>
+        <v>-127.2925559917951</v>
       </c>
       <c r="P22">
-        <v>-402.4759901187668</v>
+        <v>-426.1533396247052</v>
       </c>
       <c r="Q22">
-        <v>-370.8759901187668</v>
+        <v>-394.5533396247051</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1473030233342927</v>
+        <v>0.1485878717309293</v>
       </c>
       <c r="T22">
-        <v>1.57021948915176</v>
+        <v>1.590095685216972</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.03451891858905132</v>
+        <v>0.03287516056100125</v>
       </c>
       <c r="W22">
-        <v>0.2276604389967017</v>
+        <v>0.2280480371397159</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.1500822547350057</v>
+        <v>0.1429354807000054</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3128,22 +3128,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1652745064667745</v>
+        <v>0.1671745064667745</v>
       </c>
       <c r="C23">
-        <v>6242.932649534028</v>
+        <v>5978.808625758014</v>
       </c>
       <c r="D23">
-        <v>8542.064861648108</v>
+        <v>8408.347133687052</v>
       </c>
       <c r="E23">
-        <v>1706.902630618458</v>
+        <v>1837.308926433415</v>
       </c>
       <c r="F23">
-        <v>2738.53221211408</v>
+        <v>2868.938507929037</v>
       </c>
       <c r="G23">
         <v>439.4</v>
@@ -3164,37 +3164,37 @@
         <v>92.3</v>
       </c>
       <c r="M23">
-        <v>645.7458956165002</v>
+        <v>676.495700169667</v>
       </c>
       <c r="N23">
-        <v>-553.4458956165003</v>
+        <v>-584.195700169667</v>
       </c>
       <c r="O23">
-        <v>-127.2925559917951</v>
+        <v>-134.3650110390234</v>
       </c>
       <c r="P23">
-        <v>-426.1533396247052</v>
+        <v>-449.8306891306436</v>
       </c>
       <c r="Q23">
-        <v>-394.5533396247051</v>
+        <v>-418.2306891306436</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1485878717309293</v>
+        <v>0.1499056649582489</v>
       </c>
       <c r="T23">
-        <v>1.590095685216972</v>
+        <v>1.610481527335138</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.03287516056100125</v>
+        <v>0.03138083508095574</v>
       </c>
       <c r="W23">
-        <v>0.2280480371397159</v>
+        <v>0.2284003990879107</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.1429354807000054</v>
+        <v>0.1364384133954597</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3210,22 +3210,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1671745064667745</v>
+        <v>0.1690745064667745</v>
       </c>
       <c r="C24">
-        <v>5978.808625758014</v>
+        <v>5718.806519650269</v>
       </c>
       <c r="D24">
-        <v>8408.347133687052</v>
+        <v>8278.751323394263</v>
       </c>
       <c r="E24">
-        <v>1837.308926433415</v>
+        <v>1967.715222248371</v>
       </c>
       <c r="F24">
-        <v>2868.938507929037</v>
+        <v>2999.344803743993</v>
       </c>
       <c r="G24">
         <v>439.4</v>
@@ -3246,37 +3246,37 @@
         <v>92.3</v>
       </c>
       <c r="M24">
-        <v>676.495700169667</v>
+        <v>707.2455047228336</v>
       </c>
       <c r="N24">
-        <v>-584.195700169667</v>
+        <v>-614.9455047228337</v>
       </c>
       <c r="O24">
-        <v>-134.3650110390234</v>
+        <v>-141.4374660862518</v>
       </c>
       <c r="P24">
-        <v>-449.8306891306436</v>
+        <v>-473.5080386365819</v>
       </c>
       <c r="Q24">
-        <v>-418.2306891306436</v>
+        <v>-441.9080386365819</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1499056649582489</v>
+        <v>0.1512576865810833</v>
       </c>
       <c r="T24">
-        <v>1.610481527335138</v>
+        <v>1.631396871845984</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.03138083508095574</v>
+        <v>0.03001645094700114</v>
       </c>
       <c r="W24">
-        <v>0.2284003990879107</v>
+        <v>0.2287221208666972</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.1364384133954597</v>
+        <v>0.1305063084652223</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3292,22 +3292,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1690745064667745</v>
+        <v>0.1709745064667745</v>
       </c>
       <c r="C25">
-        <v>5718.806519650269</v>
+        <v>5462.738633800411</v>
       </c>
       <c r="D25">
-        <v>8278.751323394263</v>
+        <v>8153.08973335936</v>
       </c>
       <c r="E25">
-        <v>1967.715222248371</v>
+        <v>2098.121518063327</v>
       </c>
       <c r="F25">
-        <v>2999.344803743993</v>
+        <v>3129.751099558949</v>
       </c>
       <c r="G25">
         <v>439.4</v>
@@ -3328,37 +3328,37 @@
         <v>92.3</v>
       </c>
       <c r="M25">
-        <v>707.2455047228336</v>
+        <v>737.9953092760003</v>
       </c>
       <c r="N25">
-        <v>-614.9455047228337</v>
+        <v>-645.6953092760003</v>
       </c>
       <c r="O25">
-        <v>-141.4374660862518</v>
+        <v>-148.5099211334801</v>
       </c>
       <c r="P25">
-        <v>-473.5080386365819</v>
+        <v>-497.1853881425203</v>
       </c>
       <c r="Q25">
-        <v>-441.9080386365819</v>
+        <v>-465.5853881425202</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1512576865810833</v>
+        <v>0.1526452877203081</v>
       </c>
       <c r="T25">
-        <v>1.631396871845984</v>
+        <v>1.652862620159747</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.03001645094700114</v>
+        <v>0.02876576549087609</v>
       </c>
       <c r="W25">
-        <v>0.2287221208666972</v>
+        <v>0.2290170324972514</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.1305063084652223</v>
+        <v>0.1250685456125047</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3374,22 +3374,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1709745064667745</v>
+        <v>0.1728745064667745</v>
       </c>
       <c r="C26">
-        <v>5462.738633800411</v>
+        <v>5210.42849649831</v>
       </c>
       <c r="D26">
-        <v>8153.08973335936</v>
+        <v>8031.185891872216</v>
       </c>
       <c r="E26">
-        <v>2098.121518063327</v>
+        <v>2228.527813878283</v>
       </c>
       <c r="F26">
-        <v>3129.751099558949</v>
+        <v>3260.157395373905</v>
       </c>
       <c r="G26">
         <v>439.4</v>
@@ -3410,37 +3410,37 @@
         <v>92.3</v>
       </c>
       <c r="M26">
-        <v>737.9953092760003</v>
+        <v>768.7451138291669</v>
       </c>
       <c r="N26">
-        <v>-645.6953092760003</v>
+        <v>-676.445113829167</v>
       </c>
       <c r="O26">
-        <v>-148.5099211334801</v>
+        <v>-155.5823761807084</v>
       </c>
       <c r="P26">
-        <v>-497.1853881425203</v>
+        <v>-520.8627376484585</v>
       </c>
       <c r="Q26">
-        <v>-465.5853881425202</v>
+        <v>-489.2627376484585</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1526452877203081</v>
+        <v>0.1540698915565789</v>
       </c>
       <c r="T26">
-        <v>1.652862620159747</v>
+        <v>1.674900788428544</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.02876576549087609</v>
+        <v>0.02761513487124105</v>
       </c>
       <c r="W26">
-        <v>0.2290170324972514</v>
+        <v>0.2292883511973614</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.1250685456125047</v>
+        <v>0.1200658037880045</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3456,22 +3456,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1728745064667745</v>
+        <v>0.1747745064667745</v>
       </c>
       <c r="C27">
-        <v>5210.42849649831</v>
+        <v>4961.710034871827</v>
       </c>
       <c r="D27">
-        <v>8031.185891872216</v>
+        <v>7912.873726060688</v>
       </c>
       <c r="E27">
-        <v>2228.527813878283</v>
+        <v>2358.934109693239</v>
       </c>
       <c r="F27">
-        <v>3260.157395373905</v>
+        <v>3390.563691188861</v>
       </c>
       <c r="G27">
         <v>439.4</v>
@@ -3492,37 +3492,37 @@
         <v>92.3</v>
       </c>
       <c r="M27">
-        <v>768.7451138291669</v>
+        <v>799.4949183823336</v>
       </c>
       <c r="N27">
-        <v>-676.445113829167</v>
+        <v>-707.1949183823336</v>
       </c>
       <c r="O27">
-        <v>-155.5823761807084</v>
+        <v>-162.6548312279367</v>
       </c>
       <c r="P27">
-        <v>-520.8627376484585</v>
+        <v>-544.5400871543969</v>
       </c>
       <c r="Q27">
-        <v>-489.2627376484585</v>
+        <v>-512.9400871543969</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1540698915565789</v>
+        <v>0.1555329981992353</v>
       </c>
       <c r="T27">
-        <v>1.674900788428544</v>
+        <v>1.697534582866767</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.02761513487124105</v>
+        <v>0.02655301429927024</v>
       </c>
       <c r="W27">
-        <v>0.2292883511973614</v>
+        <v>0.2295387992282321</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.1200658037880045</v>
+        <v>0.1154478882576967</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3538,22 +3538,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1747745064667745</v>
+        <v>0.1766745064667745</v>
       </c>
       <c r="C28">
-        <v>4961.710034871827</v>
+        <v>4716.426820049481</v>
       </c>
       <c r="D28">
-        <v>7912.873726060688</v>
+        <v>7797.9968070533</v>
       </c>
       <c r="E28">
-        <v>2358.934109693239</v>
+        <v>2489.340405508196</v>
       </c>
       <c r="F28">
-        <v>3390.563691188861</v>
+        <v>3520.969987003818</v>
       </c>
       <c r="G28">
         <v>439.4</v>
@@ -3574,37 +3574,37 @@
         <v>92.3</v>
       </c>
       <c r="M28">
-        <v>799.4949183823336</v>
+        <v>830.2447229355004</v>
       </c>
       <c r="N28">
-        <v>-707.1949183823336</v>
+        <v>-737.9447229355004</v>
       </c>
       <c r="O28">
-        <v>-162.6548312279367</v>
+        <v>-169.7272862751651</v>
       </c>
       <c r="P28">
-        <v>-544.5400871543969</v>
+        <v>-568.2174366603354</v>
       </c>
       <c r="Q28">
-        <v>-512.9400871543969</v>
+        <v>-536.6174366603353</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1555329981992353</v>
+        <v>0.1570361899553892</v>
       </c>
       <c r="T28">
-        <v>1.697534582866767</v>
+        <v>1.720788481262203</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.02655301429927024</v>
+        <v>0.0255695693252232</v>
       </c>
       <c r="W28">
-        <v>0.2295387992282321</v>
+        <v>0.2297706955531124</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.1154478882576967</v>
+        <v>0.1111720405444486</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3620,22 +3620,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1766745064667745</v>
+        <v>0.1785745064667745</v>
       </c>
       <c r="C29">
-        <v>4716.426820049481</v>
+        <v>4474.431377133393</v>
       </c>
       <c r="D29">
-        <v>7797.9968070533</v>
+        <v>7686.407659952168</v>
       </c>
       <c r="E29">
-        <v>2489.340405508196</v>
+        <v>2619.746701323152</v>
       </c>
       <c r="F29">
-        <v>3520.969987003818</v>
+        <v>3651.376282818774</v>
       </c>
       <c r="G29">
         <v>439.4</v>
@@ -3656,37 +3656,37 @@
         <v>92.3</v>
       </c>
       <c r="M29">
-        <v>830.2447229355004</v>
+        <v>860.994527488667</v>
       </c>
       <c r="N29">
-        <v>-737.9447229355004</v>
+        <v>-768.6945274886671</v>
       </c>
       <c r="O29">
-        <v>-169.7272862751651</v>
+        <v>-176.7997413223934</v>
       </c>
       <c r="P29">
-        <v>-568.2174366603354</v>
+        <v>-591.8947861662737</v>
       </c>
       <c r="Q29">
-        <v>-536.6174366603353</v>
+        <v>-560.2947861662736</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1570361899553892</v>
+        <v>0.158581137038103</v>
       </c>
       <c r="T29">
-        <v>1.720788481262203</v>
+        <v>1.744688321279733</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.0255695693252232</v>
+        <v>0.02465637042075094</v>
       </c>
       <c r="W29">
-        <v>0.2297706955531124</v>
+        <v>0.2299860278547869</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.1111720405444486</v>
+        <v>0.107201610525004</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3702,22 +3702,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1785745064667745</v>
+        <v>0.1804745064667745</v>
       </c>
       <c r="C30">
-        <v>4474.431377133393</v>
+        <v>4235.58455358194</v>
       </c>
       <c r="D30">
-        <v>7686.407659952168</v>
+        <v>7577.967132215671</v>
       </c>
       <c r="E30">
-        <v>2619.746701323152</v>
+        <v>2750.152997138109</v>
       </c>
       <c r="F30">
-        <v>3651.376282818774</v>
+        <v>3781.782578633731</v>
       </c>
       <c r="G30">
         <v>439.4</v>
@@ -3738,37 +3738,37 @@
         <v>92.3</v>
       </c>
       <c r="M30">
-        <v>860.994527488667</v>
+        <v>891.7443320418338</v>
       </c>
       <c r="N30">
-        <v>-768.6945274886671</v>
+        <v>-799.4443320418338</v>
       </c>
       <c r="O30">
-        <v>-176.7997413223934</v>
+        <v>-183.8721963696218</v>
       </c>
       <c r="P30">
-        <v>-591.8947861662737</v>
+        <v>-615.5721356722121</v>
       </c>
       <c r="Q30">
-        <v>-560.2947861662736</v>
+        <v>-583.9721356722121</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.158581137038103</v>
+        <v>0.1601696037569495</v>
       </c>
       <c r="T30">
-        <v>1.744688321279733</v>
+        <v>1.769261396227335</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.02465637042075094</v>
+        <v>0.02380615075106987</v>
       </c>
       <c r="W30">
-        <v>0.2299860278547869</v>
+        <v>0.2301865096528977</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.107201610525004</v>
+        <v>0.1035050032655211</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3784,22 +3784,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1804745064667745</v>
+        <v>0.1823745064667745</v>
       </c>
       <c r="C31">
-        <v>4235.584553581941</v>
+        <v>3999.754940314159</v>
       </c>
       <c r="D31">
-        <v>7577.967132215671</v>
+        <v>7472.543814762846</v>
       </c>
       <c r="E31">
-        <v>2750.152997138108</v>
+        <v>2880.559292953064</v>
       </c>
       <c r="F31">
-        <v>3781.78257863373</v>
+        <v>3912.188874448686</v>
       </c>
       <c r="G31">
         <v>439.4</v>
@@ -3820,37 +3820,37 @@
         <v>92.3</v>
       </c>
       <c r="M31">
-        <v>891.7443320418336</v>
+        <v>922.4941365950002</v>
       </c>
       <c r="N31">
-        <v>-799.4443320418336</v>
+        <v>-830.1941365950003</v>
       </c>
       <c r="O31">
-        <v>-183.8721963696217</v>
+        <v>-190.9446514168501</v>
       </c>
       <c r="P31">
-        <v>-615.5721356722119</v>
+        <v>-639.2494851781502</v>
       </c>
       <c r="Q31">
-        <v>-583.9721356722118</v>
+        <v>-607.6494851781501</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1601696037569495</v>
+        <v>0.1618034552391916</v>
       </c>
       <c r="T31">
-        <v>1.769261396227335</v>
+        <v>1.794536559030583</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.02380615075106987</v>
+        <v>0.02301261239270088</v>
       </c>
       <c r="W31">
-        <v>0.2301865096528977</v>
+        <v>0.2303736259978011</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.1035050032655211</v>
+        <v>0.1000548364900038</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3866,22 +3866,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1823745064667745</v>
+        <v>0.1842745064667745</v>
       </c>
       <c r="C32">
-        <v>3999.754940314159</v>
+        <v>3766.818340472041</v>
       </c>
       <c r="D32">
-        <v>7472.543814762846</v>
+        <v>7370.013510735684</v>
       </c>
       <c r="E32">
-        <v>2880.559292953064</v>
+        <v>3010.965588768021</v>
       </c>
       <c r="F32">
-        <v>3912.188874448686</v>
+        <v>4042.595170263643</v>
       </c>
       <c r="G32">
         <v>439.4</v>
@@ -3902,37 +3902,37 @@
         <v>92.3</v>
       </c>
       <c r="M32">
-        <v>922.4941365950002</v>
+        <v>953.243941148167</v>
       </c>
       <c r="N32">
-        <v>-830.1941365950003</v>
+        <v>-860.943941148167</v>
       </c>
       <c r="O32">
-        <v>-190.9446514168501</v>
+        <v>-198.0171064640784</v>
       </c>
       <c r="P32">
-        <v>-639.2494851781502</v>
+        <v>-662.9268346840886</v>
       </c>
       <c r="Q32">
-        <v>-607.6494851781501</v>
+        <v>-631.3268346840886</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1618034552391916</v>
+        <v>0.1634846647354118</v>
       </c>
       <c r="T32">
-        <v>1.794536559030583</v>
+        <v>1.820544335248417</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.02301261239270088</v>
+        <v>0.02227027005745246</v>
       </c>
       <c r="W32">
-        <v>0.2303736259978011</v>
+        <v>0.2305486703204527</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.1000548364900038</v>
+        <v>0.09682726111935847</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3948,22 +3948,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1842745064667745</v>
+        <v>0.1861745064667745</v>
       </c>
       <c r="C33">
-        <v>3766.818340472041</v>
+        <v>3536.657281325382</v>
       </c>
       <c r="D33">
-        <v>7370.013510735684</v>
+        <v>7270.258747403982</v>
       </c>
       <c r="E33">
-        <v>3010.965588768021</v>
+        <v>3141.371884582977</v>
       </c>
       <c r="F33">
-        <v>4042.595170263643</v>
+        <v>4173.001466078599</v>
       </c>
       <c r="G33">
         <v>439.4</v>
@@ -3984,37 +3984,37 @@
         <v>92.3</v>
       </c>
       <c r="M33">
-        <v>953.243941148167</v>
+        <v>983.9937457013338</v>
       </c>
       <c r="N33">
-        <v>-860.943941148167</v>
+        <v>-891.6937457013338</v>
       </c>
       <c r="O33">
-        <v>-198.0171064640784</v>
+        <v>-205.0895615113068</v>
       </c>
       <c r="P33">
-        <v>-662.9268346840886</v>
+        <v>-686.604184190027</v>
       </c>
       <c r="Q33">
-        <v>-631.3268346840886</v>
+        <v>-655.004184190027</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1634846647354118</v>
+        <v>0.1652153215697561</v>
       </c>
       <c r="T33">
-        <v>1.820544335248417</v>
+        <v>1.847317046060894</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.02227027005745246</v>
+        <v>0.02157432411815707</v>
       </c>
       <c r="W33">
-        <v>0.2305486703204527</v>
+        <v>0.2307127743729386</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.09682726111935847</v>
+        <v>0.09380140920937852</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4030,22 +4030,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1861745064667745</v>
+        <v>0.1880745064667745</v>
       </c>
       <c r="C34">
-        <v>3536.657281325382</v>
+        <v>3309.1605652861</v>
       </c>
       <c r="D34">
-        <v>7270.258747403982</v>
+        <v>7173.168327179656</v>
       </c>
       <c r="E34">
-        <v>3141.371884582977</v>
+        <v>3271.778180397933</v>
       </c>
       <c r="F34">
-        <v>4173.001466078599</v>
+        <v>4303.407761893555</v>
       </c>
       <c r="G34">
         <v>439.4</v>
@@ -4066,37 +4066,37 @@
         <v>92.3</v>
       </c>
       <c r="M34">
-        <v>983.9937457013338</v>
+        <v>1014.7435502545</v>
       </c>
       <c r="N34">
-        <v>-891.6937457013338</v>
+        <v>-922.4435502545005</v>
       </c>
       <c r="O34">
-        <v>-205.0895615113068</v>
+        <v>-212.1620165585351</v>
       </c>
       <c r="P34">
-        <v>-686.604184190027</v>
+        <v>-710.2815336959653</v>
       </c>
       <c r="Q34">
-        <v>-655.004184190027</v>
+        <v>-678.6815336959653</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1652153215697561</v>
+        <v>0.1669976398021405</v>
       </c>
       <c r="T34">
-        <v>1.847317046060894</v>
+        <v>1.874888942270758</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.02157432411815707</v>
+        <v>0.02092055672063716</v>
       </c>
       <c r="W34">
-        <v>0.2307127743729386</v>
+        <v>0.2308669327252738</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.09380140920937852</v>
+        <v>0.09095894226363976</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4112,22 +4112,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1880745064667745</v>
+        <v>0.1899745064667745</v>
       </c>
       <c r="C35">
-        <v>3309.1605652861</v>
+        <v>3084.222856424261</v>
       </c>
       <c r="D35">
-        <v>7173.168327179656</v>
+        <v>7078.636914132773</v>
       </c>
       <c r="E35">
-        <v>3271.778180397933</v>
+        <v>3402.184476212889</v>
       </c>
       <c r="F35">
-        <v>4303.407761893555</v>
+        <v>4433.814057708511</v>
       </c>
       <c r="G35">
         <v>439.4</v>
@@ -4148,37 +4148,37 @@
         <v>92.3</v>
       </c>
       <c r="M35">
-        <v>1014.7435502545</v>
+        <v>1045.493354807667</v>
       </c>
       <c r="N35">
-        <v>-922.4435502545005</v>
+        <v>-953.193354807667</v>
       </c>
       <c r="O35">
-        <v>-212.1620165585351</v>
+        <v>-219.2344716057634</v>
       </c>
       <c r="P35">
-        <v>-710.2815336959653</v>
+        <v>-733.9588832019035</v>
       </c>
       <c r="Q35">
-        <v>-678.6815336959653</v>
+        <v>-702.3588832019035</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1669976398021405</v>
+        <v>0.1688339676779305</v>
       </c>
       <c r="T35">
-        <v>1.874888942270758</v>
+        <v>1.903296350486982</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.02092055672063716</v>
+        <v>0.02030524622885372</v>
       </c>
       <c r="W35">
-        <v>0.2308669327252738</v>
+        <v>0.2310120229392363</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.09095894226363976</v>
+        <v>0.08828367925588565</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4194,22 +4194,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1899745064667745</v>
+        <v>0.1918745064667745</v>
       </c>
       <c r="C36">
-        <v>3084.222856424261</v>
+        <v>2861.744299253341</v>
       </c>
       <c r="D36">
-        <v>7078.636914132773</v>
+        <v>6986.564652776809</v>
       </c>
       <c r="E36">
-        <v>3402.184476212889</v>
+        <v>3532.590772027846</v>
       </c>
       <c r="F36">
-        <v>4433.814057708511</v>
+        <v>4564.220353523468</v>
       </c>
       <c r="G36">
         <v>439.4</v>
@@ -4230,37 +4230,37 @@
         <v>92.3</v>
       </c>
       <c r="M36">
-        <v>1045.493354807667</v>
+        <v>1076.243159360834</v>
       </c>
       <c r="N36">
-        <v>-953.193354807667</v>
+        <v>-983.9431593608338</v>
       </c>
       <c r="O36">
-        <v>-219.2344716057634</v>
+        <v>-226.3069266529918</v>
       </c>
       <c r="P36">
-        <v>-733.9588832019035</v>
+        <v>-757.6362327078421</v>
       </c>
       <c r="Q36">
-        <v>-702.3588832019035</v>
+        <v>-726.036232707842</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1688339676779305</v>
+        <v>0.1707267979498987</v>
       </c>
       <c r="T36">
-        <v>1.903296350486982</v>
+        <v>1.932577832802166</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.02030524622885372</v>
+        <v>0.01972509633660075</v>
       </c>
       <c r="W36">
-        <v>0.2310120229392363</v>
+        <v>0.2311488222838295</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.08828367925588565</v>
+        <v>0.08576128842000319</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4276,22 +4276,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1918745064667745</v>
+        <v>0.1937745064667745</v>
       </c>
       <c r="C37">
-        <v>2861.744299253341</v>
+        <v>2641.630166884413</v>
       </c>
       <c r="D37">
-        <v>6986.564652776809</v>
+        <v>6896.856816222838</v>
       </c>
       <c r="E37">
-        <v>3532.590772027846</v>
+        <v>3662.997067842802</v>
       </c>
       <c r="F37">
-        <v>4564.220353523468</v>
+        <v>4694.626649338424</v>
       </c>
       <c r="G37">
         <v>439.4</v>
@@ -4312,37 +4312,37 @@
         <v>92.3</v>
       </c>
       <c r="M37">
-        <v>1076.243159360834</v>
+        <v>1106.992963914</v>
       </c>
       <c r="N37">
-        <v>-983.9431593608338</v>
+        <v>-1014.692963914</v>
       </c>
       <c r="O37">
-        <v>-226.3069266529918</v>
+        <v>-233.3793817002201</v>
       </c>
       <c r="P37">
-        <v>-757.6362327078421</v>
+        <v>-781.3135822137803</v>
       </c>
       <c r="Q37">
-        <v>-726.036232707842</v>
+        <v>-749.7135822137802</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1707267979498987</v>
+        <v>0.1726787791678658</v>
       </c>
       <c r="T37">
-        <v>1.932577832802166</v>
+        <v>1.9627743614397</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.01972509633660075</v>
+        <v>0.0191771769939174</v>
       </c>
       <c r="W37">
-        <v>0.2311488222838295</v>
+        <v>0.2312780216648343</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.08576128842000319</v>
+        <v>0.0833790304083365</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4358,22 +4358,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1937745064667745</v>
+        <v>0.1956745064667745</v>
       </c>
       <c r="C38">
-        <v>2641.630166884413</v>
+        <v>2423.79053594299</v>
       </c>
       <c r="D38">
-        <v>6896.856816222838</v>
+        <v>6809.42348109637</v>
       </c>
       <c r="E38">
-        <v>3662.997067842802</v>
+        <v>3793.403363657758</v>
       </c>
       <c r="F38">
-        <v>4694.626649338424</v>
+        <v>4825.03294515338</v>
       </c>
       <c r="G38">
         <v>439.4</v>
@@ -4394,37 +4394,37 @@
         <v>92.3</v>
       </c>
       <c r="M38">
-        <v>1106.992963914</v>
+        <v>1137.742768467167</v>
       </c>
       <c r="N38">
-        <v>-1014.692963914</v>
+        <v>-1045.442768467167</v>
       </c>
       <c r="O38">
-        <v>-233.3793817002201</v>
+        <v>-240.4518367474484</v>
       </c>
       <c r="P38">
-        <v>-781.3135822137803</v>
+        <v>-804.9909317197187</v>
       </c>
       <c r="Q38">
-        <v>-749.7135822137802</v>
+        <v>-773.3909317197187</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1726787791678658</v>
+        <v>0.1746927280435463</v>
       </c>
       <c r="T38">
-        <v>1.9627743614397</v>
+        <v>1.993929510033981</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.0191771769939174</v>
+        <v>0.01865887491300071</v>
       </c>
       <c r="W38">
-        <v>0.2312780216648343</v>
+        <v>0.2314002372955145</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.0833790304083365</v>
+        <v>0.08112554310000308</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4440,22 +4440,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1956745064667745</v>
+        <v>0.1975745064667745</v>
       </c>
       <c r="C39">
-        <v>2423.79053594299</v>
+        <v>2208.139985903326</v>
       </c>
       <c r="D39">
-        <v>6809.42348109637</v>
+        <v>6724.179226871663</v>
       </c>
       <c r="E39">
-        <v>3793.403363657758</v>
+        <v>3923.809659472714</v>
       </c>
       <c r="F39">
-        <v>4825.03294515338</v>
+        <v>4955.439240968336</v>
       </c>
       <c r="G39">
         <v>439.4</v>
@@ -4476,37 +4476,37 @@
         <v>92.3</v>
       </c>
       <c r="M39">
-        <v>1137.742768467167</v>
+        <v>1168.492573020334</v>
       </c>
       <c r="N39">
-        <v>-1045.442768467167</v>
+        <v>-1076.192573020334</v>
       </c>
       <c r="O39">
-        <v>-240.4518367474484</v>
+        <v>-247.5242917946767</v>
       </c>
       <c r="P39">
-        <v>-804.9909317197187</v>
+        <v>-828.6682812256569</v>
       </c>
       <c r="Q39">
-        <v>-773.3909317197187</v>
+        <v>-797.0682812256568</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1746927280435463</v>
+        <v>0.1767716430119906</v>
       </c>
       <c r="T39">
-        <v>1.993929510033981</v>
+        <v>2.026089663421625</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.01865887491300071</v>
+        <v>0.01816785188897438</v>
       </c>
       <c r="W39">
-        <v>0.2314002372955145</v>
+        <v>0.2315160205245798</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.08112554310000308</v>
+        <v>0.0789906603868451</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4522,22 +4522,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1975745064667745</v>
+        <v>0.1994745064667745</v>
       </c>
       <c r="C40">
-        <v>2208.139985903326</v>
+        <v>1994.597320726948</v>
       </c>
       <c r="D40">
-        <v>6724.179226871663</v>
+        <v>6641.042857510241</v>
       </c>
       <c r="E40">
-        <v>3923.809659472714</v>
+        <v>4054.21595528767</v>
       </c>
       <c r="F40">
-        <v>4955.439240968336</v>
+        <v>5085.845536783292</v>
       </c>
       <c r="G40">
         <v>439.4</v>
@@ -4558,37 +4558,37 @@
         <v>92.3</v>
       </c>
       <c r="M40">
-        <v>1168.492573020334</v>
+        <v>1199.2423775735</v>
       </c>
       <c r="N40">
-        <v>-1076.192573020334</v>
+        <v>-1106.9423775735</v>
       </c>
       <c r="O40">
-        <v>-247.5242917946767</v>
+        <v>-254.5967468419051</v>
       </c>
       <c r="P40">
-        <v>-828.6682812256569</v>
+        <v>-852.3456307315953</v>
       </c>
       <c r="Q40">
-        <v>-797.0682812256568</v>
+        <v>-820.7456307315953</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1767716430119906</v>
+        <v>0.1789187191269412</v>
       </c>
       <c r="T40">
-        <v>2.026089663421625</v>
+        <v>2.059304248067882</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.01816785188897438</v>
+        <v>0.01770200953284683</v>
       </c>
       <c r="W40">
-        <v>0.2315160205245798</v>
+        <v>0.2316258661521547</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.0789906603868451</v>
+        <v>0.07696525883846439</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4604,22 +4604,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1994745064667745</v>
+        <v>0.2013745064667745</v>
       </c>
       <c r="C41">
-        <v>1994.597320726948</v>
+        <v>1783.085310898594</v>
       </c>
       <c r="D41">
-        <v>6641.042857510241</v>
+        <v>6559.937143496843</v>
       </c>
       <c r="E41">
-        <v>4054.21595528767</v>
+        <v>4184.622251102627</v>
       </c>
       <c r="F41">
-        <v>5085.845536783292</v>
+        <v>5216.251832598249</v>
       </c>
       <c r="G41">
         <v>439.4</v>
@@ -4640,37 +4640,37 @@
         <v>92.3</v>
       </c>
       <c r="M41">
-        <v>1199.2423775735</v>
+        <v>1229.992182126667</v>
       </c>
       <c r="N41">
-        <v>-1106.9423775735</v>
+        <v>-1137.692182126667</v>
       </c>
       <c r="O41">
-        <v>-254.5967468419051</v>
+        <v>-261.6692018891334</v>
       </c>
       <c r="P41">
-        <v>-852.3456307315953</v>
+        <v>-876.0229802375337</v>
       </c>
       <c r="Q41">
-        <v>-820.7456307315953</v>
+        <v>-844.4229802375337</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1789187191269412</v>
+        <v>0.1811373644457236</v>
       </c>
       <c r="T41">
-        <v>2.059304248067882</v>
+        <v>2.09362598553568</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.01770200953284683</v>
+        <v>0.01725945929452566</v>
       </c>
       <c r="W41">
-        <v>0.2316258661521547</v>
+        <v>0.2317302194983508</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.07696525883846439</v>
+        <v>0.07504112736750279</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4686,22 +4686,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2013745064667745</v>
+        <v>0.2032745064667745</v>
       </c>
       <c r="C42">
-        <v>1783.085310898594</v>
+        <v>1573.530454136894</v>
       </c>
       <c r="D42">
-        <v>6559.937143496843</v>
+        <v>6480.7885825501</v>
       </c>
       <c r="E42">
-        <v>4184.622251102627</v>
+        <v>4315.028546917583</v>
       </c>
       <c r="F42">
-        <v>5216.251832598249</v>
+        <v>5346.658128413205</v>
       </c>
       <c r="G42">
         <v>439.4</v>
@@ -4722,37 +4722,37 @@
         <v>92.3</v>
       </c>
       <c r="M42">
-        <v>1229.992182126667</v>
+        <v>1260.741986679834</v>
       </c>
       <c r="N42">
-        <v>-1137.692182126667</v>
+        <v>-1168.441986679834</v>
       </c>
       <c r="O42">
-        <v>-261.6692018891334</v>
+        <v>-268.7416569363618</v>
       </c>
       <c r="P42">
-        <v>-876.0229802375337</v>
+        <v>-899.7003297434721</v>
       </c>
       <c r="Q42">
-        <v>-844.4229802375337</v>
+        <v>-868.1003297434721</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1811373644457236</v>
+        <v>0.1834312180803969</v>
       </c>
       <c r="T42">
-        <v>2.09362598553568</v>
+        <v>2.1291111717312</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.01725945929452566</v>
+        <v>0.01683849687270796</v>
       </c>
       <c r="W42">
-        <v>0.2317302194983508</v>
+        <v>0.2318294824374155</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.07504112736750279</v>
+        <v>0.07321085596829546</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4768,22 +4768,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2032745064667745</v>
+        <v>0.2051745064667745</v>
       </c>
       <c r="C43">
-        <v>1573.530454136894</v>
+        <v>1365.862753221291</v>
       </c>
       <c r="D43">
-        <v>6480.7885825501</v>
+        <v>6403.527177449453</v>
       </c>
       <c r="E43">
-        <v>4315.028546917583</v>
+        <v>4445.434842732539</v>
       </c>
       <c r="F43">
-        <v>5346.658128413205</v>
+        <v>5477.064424228161</v>
       </c>
       <c r="G43">
         <v>439.4</v>
@@ -4804,37 +4804,37 @@
         <v>92.3</v>
       </c>
       <c r="M43">
-        <v>1260.741986679834</v>
+        <v>1291.491791233</v>
       </c>
       <c r="N43">
-        <v>-1168.441986679834</v>
+        <v>-1199.191791233</v>
       </c>
       <c r="O43">
-        <v>-268.7416569363618</v>
+        <v>-275.8141119835901</v>
       </c>
       <c r="P43">
-        <v>-899.7003297434721</v>
+        <v>-923.3776792494103</v>
       </c>
       <c r="Q43">
-        <v>-868.1003297434721</v>
+        <v>-891.7776792494103</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1834312180803969</v>
+        <v>0.1858041701162658</v>
       </c>
       <c r="T43">
-        <v>2.1291111717312</v>
+        <v>2.16581998503691</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.01683849687270796</v>
+        <v>0.01643758028050063</v>
       </c>
       <c r="W43">
-        <v>0.2318294824374155</v>
+        <v>0.231924018569858</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.07321085596829546</v>
+        <v>0.0714677403500027</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4850,22 +4850,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2051745064667745</v>
+        <v>0.2070745064667745</v>
       </c>
       <c r="C44">
-        <v>1365.862753221292</v>
+        <v>1160.015509523722</v>
       </c>
       <c r="D44">
-        <v>6403.527177449453</v>
+        <v>6328.086229566839</v>
       </c>
       <c r="E44">
-        <v>4445.434842732539</v>
+        <v>4575.841138547495</v>
       </c>
       <c r="F44">
-        <v>5477.064424228161</v>
+        <v>5607.470720043117</v>
       </c>
       <c r="G44">
         <v>439.4</v>
@@ -4886,37 +4886,37 @@
         <v>92.3</v>
       </c>
       <c r="M44">
-        <v>1291.491791233</v>
+        <v>1322.241595786167</v>
       </c>
       <c r="N44">
-        <v>-1199.191791233</v>
+        <v>-1229.941595786167</v>
       </c>
       <c r="O44">
-        <v>-275.8141119835901</v>
+        <v>-282.8865670308184</v>
       </c>
       <c r="P44">
-        <v>-923.3776792494103</v>
+        <v>-947.0550287553485</v>
       </c>
       <c r="Q44">
-        <v>-891.7776792494103</v>
+        <v>-915.4550287553485</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1858041701162657</v>
+        <v>0.1882603836270774</v>
       </c>
       <c r="T44">
-        <v>2.16581998503691</v>
+        <v>2.203816826879663</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.01643758028050063</v>
+        <v>0.01605531097165178</v>
       </c>
       <c r="W44">
-        <v>0.231924018569858</v>
+        <v>0.2320141576728845</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.0714677403500027</v>
+        <v>0.06980569987674679</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4932,22 +4932,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2070745064667745</v>
+        <v>0.2089745064667745</v>
       </c>
       <c r="C45">
-        <v>1160.015509523722</v>
+        <v>955.9251309649626</v>
       </c>
       <c r="D45">
-        <v>6328.086229566839</v>
+        <v>6254.402146823037</v>
       </c>
       <c r="E45">
-        <v>4575.841138547495</v>
+        <v>4706.247434362452</v>
       </c>
       <c r="F45">
-        <v>5607.470720043117</v>
+        <v>5737.877015858074</v>
       </c>
       <c r="G45">
         <v>439.4</v>
@@ -4968,37 +4968,37 @@
         <v>92.3</v>
       </c>
       <c r="M45">
-        <v>1322.241595786167</v>
+        <v>1352.991400339334</v>
       </c>
       <c r="N45">
-        <v>-1229.941595786167</v>
+        <v>-1260.691400339334</v>
       </c>
       <c r="O45">
-        <v>-282.8865670308184</v>
+        <v>-289.9590220780468</v>
       </c>
       <c r="P45">
-        <v>-947.0550287553485</v>
+        <v>-970.7323782612872</v>
       </c>
       <c r="Q45">
-        <v>-915.4550287553485</v>
+        <v>-939.1323782612872</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1882603836270774</v>
+        <v>0.1908043190489895</v>
       </c>
       <c r="T45">
-        <v>2.203816826879663</v>
+        <v>2.243170698788228</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.01605531097165178</v>
+        <v>0.01569041754047787</v>
       </c>
       <c r="W45">
-        <v>0.2320141576728845</v>
+        <v>0.2321001995439553</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.06980569987674679</v>
+        <v>0.06821920669772985</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5014,22 +5014,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2089745064667745</v>
+        <v>0.2108745064667745</v>
       </c>
       <c r="C46">
-        <v>955.9251309649626</v>
+        <v>753.5309532334531</v>
       </c>
       <c r="D46">
-        <v>6254.402146823037</v>
+        <v>6182.414264906483</v>
       </c>
       <c r="E46">
-        <v>4706.247434362452</v>
+        <v>4836.653730177408</v>
       </c>
       <c r="F46">
-        <v>5737.877015858074</v>
+        <v>5868.28331167303</v>
       </c>
       <c r="G46">
         <v>439.4</v>
@@ -5050,37 +5050,37 @@
         <v>92.3</v>
       </c>
       <c r="M46">
-        <v>1352.991400339334</v>
+        <v>1383.7412048925</v>
       </c>
       <c r="N46">
-        <v>-1260.691400339334</v>
+        <v>-1291.441204892501</v>
       </c>
       <c r="O46">
-        <v>-289.9590220780468</v>
+        <v>-297.0314771252752</v>
       </c>
       <c r="P46">
-        <v>-970.7323782612872</v>
+        <v>-994.4097277672254</v>
       </c>
       <c r="Q46">
-        <v>-939.1323782612872</v>
+        <v>-962.8097277672254</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1908043190489895</v>
+        <v>0.1934407612135166</v>
       </c>
       <c r="T46">
-        <v>2.243170698788228</v>
+        <v>2.283955620584378</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.01569041754047787</v>
+        <v>0.01534174159513392</v>
       </c>
       <c r="W46">
-        <v>0.2321001995439553</v>
+        <v>0.2321824173318674</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.06821920669772985</v>
+        <v>0.0667032243266692</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5096,22 +5096,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2108745064667745</v>
+        <v>0.2127745064667745</v>
       </c>
       <c r="C47">
-        <v>753.5309532334531</v>
+        <v>552.7750732102031</v>
       </c>
       <c r="D47">
-        <v>6182.414264906483</v>
+        <v>6112.064680698189</v>
       </c>
       <c r="E47">
-        <v>4836.653730177408</v>
+        <v>4967.060025992364</v>
       </c>
       <c r="F47">
-        <v>5868.28331167303</v>
+        <v>5998.689607487986</v>
       </c>
       <c r="G47">
         <v>439.4</v>
@@ -5132,37 +5132,37 @@
         <v>92.3</v>
       </c>
       <c r="M47">
-        <v>1383.7412048925</v>
+        <v>1414.491009445667</v>
       </c>
       <c r="N47">
-        <v>-1291.441204892501</v>
+        <v>-1322.191009445667</v>
       </c>
       <c r="O47">
-        <v>-297.0314771252752</v>
+        <v>-304.1039321725035</v>
       </c>
       <c r="P47">
-        <v>-994.4097277672254</v>
+        <v>-1018.087077273164</v>
       </c>
       <c r="Q47">
-        <v>-962.8097277672254</v>
+        <v>-986.4870772731638</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1934407612135166</v>
+        <v>0.1961748493841373</v>
       </c>
       <c r="T47">
-        <v>2.283955620584378</v>
+        <v>2.326251095039644</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.01534174159513392</v>
+        <v>0.01500822547350057</v>
       </c>
       <c r="W47">
-        <v>0.2321824173318674</v>
+        <v>0.2322610604333486</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.0667032243266692</v>
+        <v>0.06525315423261113</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5178,22 +5178,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2127745064667745</v>
+        <v>0.2146745064667745</v>
       </c>
       <c r="C48">
-        <v>552.7750732102031</v>
+        <v>353.6021936385005</v>
       </c>
       <c r="D48">
-        <v>6112.064680698189</v>
+        <v>6043.298096941443</v>
       </c>
       <c r="E48">
-        <v>4967.060025992364</v>
+        <v>5097.46632180732</v>
       </c>
       <c r="F48">
-        <v>5998.689607487986</v>
+        <v>6129.095903302942</v>
       </c>
       <c r="G48">
         <v>439.4</v>
@@ -5214,37 +5214,37 @@
         <v>92.3</v>
       </c>
       <c r="M48">
-        <v>1414.491009445667</v>
+        <v>1445.240813998834</v>
       </c>
       <c r="N48">
-        <v>-1322.191009445667</v>
+        <v>-1352.940813998834</v>
       </c>
       <c r="O48">
-        <v>-304.1039321725035</v>
+        <v>-311.1763872197318</v>
       </c>
       <c r="P48">
-        <v>-1018.087077273164</v>
+        <v>-1041.764426779102</v>
       </c>
       <c r="Q48">
-        <v>-986.4870772731638</v>
+        <v>-1010.164426779102</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1961748493841373</v>
+        <v>0.199012110693272</v>
       </c>
       <c r="T48">
-        <v>2.326251095039644</v>
+        <v>2.370142625134732</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.01500822547350057</v>
+        <v>0.01468890152725588</v>
       </c>
       <c r="W48">
-        <v>0.2322610604333486</v>
+        <v>0.2323363570198731</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.06525315423261113</v>
+        <v>0.06386478924893857</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5260,22 +5260,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2146745064667745</v>
+        <v>0.2165745064667745</v>
       </c>
       <c r="C49">
-        <v>353.6021936385005</v>
+        <v>155.959478162612</v>
       </c>
       <c r="D49">
-        <v>6043.298096941443</v>
+        <v>5976.061677280511</v>
       </c>
       <c r="E49">
-        <v>5097.46632180732</v>
+        <v>5227.872617622276</v>
       </c>
       <c r="F49">
-        <v>6129.095903302942</v>
+        <v>6259.502199117898</v>
       </c>
       <c r="G49">
         <v>439.4</v>
@@ -5296,37 +5296,37 @@
         <v>92.3</v>
       </c>
       <c r="M49">
-        <v>1445.240813998834</v>
+        <v>1475.990618552001</v>
       </c>
       <c r="N49">
-        <v>-1352.940813998834</v>
+        <v>-1383.690618552001</v>
       </c>
       <c r="O49">
-        <v>-311.1763872197318</v>
+        <v>-318.2488422669601</v>
       </c>
       <c r="P49">
-        <v>-1041.764426779102</v>
+        <v>-1065.441776285041</v>
       </c>
       <c r="Q49">
-        <v>-1010.164426779102</v>
+        <v>-1033.841776285041</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.199012110693272</v>
+        <v>0.2019584974373733</v>
       </c>
       <c r="T49">
-        <v>2.370142625134732</v>
+        <v>2.415722291002707</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.01468890152725588</v>
+        <v>0.01438288274543805</v>
       </c>
       <c r="W49">
-        <v>0.2323363570198731</v>
+        <v>0.2324085162486257</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.06386478924893857</v>
+        <v>0.06253427280625234</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5342,22 +5342,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2165745064667745</v>
+        <v>0.2184745064667745</v>
       </c>
       <c r="C50">
-        <v>155.9594781626129</v>
+        <v>-40.20358406312607</v>
       </c>
       <c r="D50">
-        <v>5976.061677280512</v>
+        <v>5910.304910869729</v>
       </c>
       <c r="E50">
-        <v>5227.872617622276</v>
+        <v>5358.278913437232</v>
       </c>
       <c r="F50">
-        <v>6259.502199117898</v>
+        <v>6389.908494932854</v>
       </c>
       <c r="G50">
         <v>439.4</v>
@@ -5378,37 +5378,37 @@
         <v>92.3</v>
       </c>
       <c r="M50">
-        <v>1475.990618552001</v>
+        <v>1506.740423105167</v>
       </c>
       <c r="N50">
-        <v>-1383.690618552001</v>
+        <v>-1414.440423105167</v>
       </c>
       <c r="O50">
-        <v>-318.2488422669601</v>
+        <v>-325.3212973141885</v>
       </c>
       <c r="P50">
-        <v>-1065.441776285041</v>
+        <v>-1089.119125790979</v>
       </c>
       <c r="Q50">
-        <v>-1033.841776285041</v>
+        <v>-1057.519125790979</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2019584974373733</v>
+        <v>0.2050204287596748</v>
       </c>
       <c r="T50">
-        <v>2.415722291002707</v>
+        <v>2.463089394747858</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.01438288274543805</v>
+        <v>0.01408935452614339</v>
       </c>
       <c r="W50">
-        <v>0.2324085162486257</v>
+        <v>0.2324777302027354</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.06253427280625234</v>
+        <v>0.06125806315714521</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5424,22 +5424,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2184745064667745</v>
+        <v>0.2203745064667745</v>
       </c>
       <c r="C51">
-        <v>-40.20358406312607</v>
+        <v>-234.9353049239762</v>
       </c>
       <c r="D51">
-        <v>5910.304910869729</v>
+        <v>5845.979485823835</v>
       </c>
       <c r="E51">
-        <v>5358.278913437232</v>
+        <v>5488.685209252189</v>
       </c>
       <c r="F51">
-        <v>6389.908494932854</v>
+        <v>6520.314790747811</v>
       </c>
       <c r="G51">
         <v>439.4</v>
@@ -5460,37 +5460,37 @@
         <v>92.3</v>
       </c>
       <c r="M51">
-        <v>1506.740423105167</v>
+        <v>1537.490227658334</v>
       </c>
       <c r="N51">
-        <v>-1414.440423105167</v>
+        <v>-1445.190227658334</v>
       </c>
       <c r="O51">
-        <v>-325.3212973141885</v>
+        <v>-332.3937523614168</v>
       </c>
       <c r="P51">
-        <v>-1089.119125790979</v>
+        <v>-1112.796475296917</v>
       </c>
       <c r="Q51">
-        <v>-1057.519125790979</v>
+        <v>-1081.196475296917</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2050204287596748</v>
+        <v>0.2082048373348683</v>
       </c>
       <c r="T51">
-        <v>2.463089394747858</v>
+        <v>2.512351182642816</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.01408935452614339</v>
+        <v>0.01380756743562053</v>
       </c>
       <c r="W51">
-        <v>0.2324777302027354</v>
+        <v>0.2325441755986807</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.06125806315714521</v>
+        <v>0.06003290189400223</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5506,22 +5506,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2203745064667745</v>
+        <v>0.2222745064667745</v>
       </c>
       <c r="C52">
-        <v>-234.9353049239762</v>
+        <v>-428.2819157195372</v>
       </c>
       <c r="D52">
-        <v>5845.979485823835</v>
+        <v>5783.03917084323</v>
       </c>
       <c r="E52">
-        <v>5488.685209252189</v>
+        <v>5619.091505067145</v>
       </c>
       <c r="F52">
-        <v>6520.314790747811</v>
+        <v>6650.721086562767</v>
       </c>
       <c r="G52">
         <v>439.4</v>
@@ -5542,37 +5542,37 @@
         <v>92.3</v>
       </c>
       <c r="M52">
-        <v>1537.490227658334</v>
+        <v>1568.2400322115</v>
       </c>
       <c r="N52">
-        <v>-1445.190227658334</v>
+        <v>-1475.9400322115</v>
       </c>
       <c r="O52">
-        <v>-332.3937523614168</v>
+        <v>-339.4662074086451</v>
       </c>
       <c r="P52">
-        <v>-1112.796475296917</v>
+        <v>-1136.473824802855</v>
       </c>
       <c r="Q52">
-        <v>-1081.196475296917</v>
+        <v>-1104.873824802855</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2082048373348683</v>
+        <v>0.2115192217702738</v>
       </c>
       <c r="T52">
-        <v>2.512351182642816</v>
+        <v>2.563623655757975</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.01380756743562053</v>
+        <v>0.01353683081923581</v>
       </c>
       <c r="W52">
-        <v>0.2325441755986807</v>
+        <v>0.2326080152928242</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.06003290189400223</v>
+        <v>0.05885578617059051</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5588,22 +5588,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2222745064667745</v>
+        <v>0.2241745064667745</v>
       </c>
       <c r="C53">
-        <v>-428.2819157195372</v>
+        <v>-620.2876779730941</v>
       </c>
       <c r="D53">
-        <v>5783.03917084323</v>
+        <v>5721.439704404629</v>
       </c>
       <c r="E53">
-        <v>5619.091505067145</v>
+        <v>5749.497800882101</v>
       </c>
       <c r="F53">
-        <v>6650.721086562767</v>
+        <v>6781.127382377723</v>
       </c>
       <c r="G53">
         <v>439.4</v>
@@ -5624,37 +5624,37 @@
         <v>92.3</v>
       </c>
       <c r="M53">
-        <v>1568.2400322115</v>
+        <v>1598.989836764667</v>
       </c>
       <c r="N53">
-        <v>-1475.9400322115</v>
+        <v>-1506.689836764667</v>
       </c>
       <c r="O53">
-        <v>-339.4662074086451</v>
+        <v>-346.5386624558735</v>
       </c>
       <c r="P53">
-        <v>-1136.473824802855</v>
+        <v>-1160.151174308794</v>
       </c>
       <c r="Q53">
-        <v>-1104.873824802855</v>
+        <v>-1128.551174308794</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2115192217702738</v>
+        <v>0.2149717055571545</v>
       </c>
       <c r="T53">
-        <v>2.563623655757975</v>
+        <v>2.6170324819196</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.01353683081923581</v>
+        <v>0.01327650714963512</v>
       </c>
       <c r="W53">
-        <v>0.2326080152928242</v>
+        <v>0.232669399614116</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.05885578617059051</v>
+        <v>0.05772394412884829</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5670,22 +5670,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2241745064667745</v>
+        <v>0.2260745064667745</v>
       </c>
       <c r="C54">
-        <v>-620.2876779730941</v>
+        <v>-810.9949872337456</v>
       </c>
       <c r="D54">
-        <v>5721.439704404629</v>
+        <v>5661.138690958935</v>
       </c>
       <c r="E54">
-        <v>5749.497800882101</v>
+        <v>5879.904096697058</v>
       </c>
       <c r="F54">
-        <v>6781.127382377723</v>
+        <v>6911.53367819268</v>
       </c>
       <c r="G54">
         <v>439.4</v>
@@ -5706,37 +5706,37 @@
         <v>92.3</v>
       </c>
       <c r="M54">
-        <v>1598.989836764667</v>
+        <v>1629.739641317834</v>
       </c>
       <c r="N54">
-        <v>-1506.689836764667</v>
+        <v>-1537.439641317834</v>
       </c>
       <c r="O54">
-        <v>-346.5386624558735</v>
+        <v>-353.6111175031018</v>
       </c>
       <c r="P54">
-        <v>-1160.151174308794</v>
+        <v>-1183.828523814732</v>
       </c>
       <c r="Q54">
-        <v>-1128.551174308794</v>
+        <v>-1152.228523814732</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2149717055571545</v>
+        <v>0.2185711035477322</v>
       </c>
       <c r="T54">
-        <v>2.6170324819196</v>
+        <v>2.672714024088102</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.01327650714963512</v>
+        <v>0.01302600701473634</v>
       </c>
       <c r="W54">
-        <v>0.232669399614116</v>
+        <v>0.2327284675459252</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.05772394412884829</v>
+        <v>0.05663481310754925</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5752,22 +5752,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2260745064667745</v>
+        <v>0.2279745064667745</v>
       </c>
       <c r="C55">
-        <v>-810.9949872337456</v>
+        <v>-1000.44447038284</v>
       </c>
       <c r="D55">
-        <v>5661.138690958935</v>
+        <v>5602.095503624796</v>
       </c>
       <c r="E55">
-        <v>5879.904096697058</v>
+        <v>6010.310392512014</v>
       </c>
       <c r="F55">
-        <v>6911.53367819268</v>
+        <v>7041.939974007636</v>
       </c>
       <c r="G55">
         <v>439.4</v>
@@ -5788,37 +5788,37 @@
         <v>92.3</v>
       </c>
       <c r="M55">
-        <v>1629.739641317834</v>
+        <v>1660.489445871001</v>
       </c>
       <c r="N55">
-        <v>-1537.439641317834</v>
+        <v>-1568.189445871001</v>
       </c>
       <c r="O55">
-        <v>-353.6111175031018</v>
+        <v>-360.6835725503302</v>
       </c>
       <c r="P55">
-        <v>-1183.828523814732</v>
+        <v>-1207.505873320671</v>
       </c>
       <c r="Q55">
-        <v>-1152.228523814732</v>
+        <v>-1175.905873320671</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2185711035477322</v>
+        <v>0.2223269971031177</v>
       </c>
       <c r="T55">
-        <v>2.672714024088102</v>
+        <v>2.730816502872626</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.01302600701473634</v>
+        <v>0.0127847846626116</v>
       </c>
       <c r="W55">
-        <v>0.2327284675459252</v>
+        <v>0.2327853477765562</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.05663481310754925</v>
+        <v>0.05558602027222426</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5834,22 +5834,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2279745064667745</v>
+        <v>0.2298745064667745</v>
       </c>
       <c r="C56">
-        <v>-1000.44447038284</v>
+        <v>-1188.675076914111</v>
       </c>
       <c r="D56">
-        <v>5602.095503624796</v>
+        <v>5544.271192908482</v>
       </c>
       <c r="E56">
-        <v>6010.310392512014</v>
+        <v>6140.71668832697</v>
       </c>
       <c r="F56">
-        <v>7041.939974007636</v>
+        <v>7172.346269822592</v>
       </c>
       <c r="G56">
         <v>439.4</v>
@@ -5870,37 +5870,37 @@
         <v>92.3</v>
       </c>
       <c r="M56">
-        <v>1660.489445871001</v>
+        <v>1691.239250424167</v>
       </c>
       <c r="N56">
-        <v>-1568.189445871001</v>
+        <v>-1598.939250424167</v>
       </c>
       <c r="O56">
-        <v>-360.6835725503302</v>
+        <v>-367.7560275975585</v>
       </c>
       <c r="P56">
-        <v>-1207.505873320671</v>
+        <v>-1231.183222826609</v>
       </c>
       <c r="Q56">
-        <v>-1175.905873320671</v>
+        <v>-1199.583222826609</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2223269971031177</v>
+        <v>0.2262498192609648</v>
       </c>
       <c r="T56">
-        <v>2.730816502872626</v>
+        <v>2.791501314047573</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.0127847846626116</v>
+        <v>0.0125523340323823</v>
       </c>
       <c r="W56">
-        <v>0.2327853477765562</v>
+        <v>0.2328401596351642</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.05558602027222426</v>
+        <v>0.05457536535818386</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5916,22 +5916,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2298745064667745</v>
+        <v>0.2317745064667745</v>
       </c>
       <c r="C57">
-        <v>-1188.675076914111</v>
+        <v>-1375.724164618439</v>
       </c>
       <c r="D57">
-        <v>5544.271192908482</v>
+        <v>5487.628401019109</v>
       </c>
       <c r="E57">
-        <v>6140.71668832697</v>
+        <v>6271.122984141926</v>
       </c>
       <c r="F57">
-        <v>7172.346269822592</v>
+        <v>7302.752565637548</v>
       </c>
       <c r="G57">
         <v>439.4</v>
@@ -5952,37 +5952,37 @@
         <v>92.3</v>
       </c>
       <c r="M57">
-        <v>1691.239250424167</v>
+        <v>1721.989054977334</v>
       </c>
       <c r="N57">
-        <v>-1598.939250424167</v>
+        <v>-1629.689054977334</v>
       </c>
       <c r="O57">
-        <v>-367.7560275975585</v>
+        <v>-374.8284826447868</v>
       </c>
       <c r="P57">
-        <v>-1231.183222826609</v>
+        <v>-1254.860572332547</v>
       </c>
       <c r="Q57">
-        <v>-1199.583222826609</v>
+        <v>-1223.260572332547</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2262498192609648</v>
+        <v>0.2303509515168958</v>
       </c>
       <c r="T57">
-        <v>2.791501314047573</v>
+        <v>2.854944525730473</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.0125523340323823</v>
+        <v>0.01232818521037547</v>
       </c>
       <c r="W57">
-        <v>0.2328401596351642</v>
+        <v>0.2328930139273935</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.05457536535818386</v>
+        <v>0.05360080526250199</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5998,22 +5998,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2317745064667745</v>
+        <v>0.2336745064667745</v>
       </c>
       <c r="C58">
-        <v>-1375.724164618439</v>
+        <v>-1561.62758006937</v>
       </c>
       <c r="D58">
-        <v>5487.628401019109</v>
+        <v>5432.131281383135</v>
       </c>
       <c r="E58">
-        <v>6271.122984141926</v>
+        <v>6401.529279956882</v>
       </c>
       <c r="F58">
-        <v>7302.752565637548</v>
+        <v>7433.158861452504</v>
       </c>
       <c r="G58">
         <v>439.4</v>
@@ -6034,37 +6034,37 @@
         <v>92.3</v>
       </c>
       <c r="M58">
-        <v>1721.989054977334</v>
+        <v>1752.738859530501</v>
       </c>
       <c r="N58">
-        <v>-1629.689054977334</v>
+        <v>-1660.438859530501</v>
       </c>
       <c r="O58">
-        <v>-374.8284826447868</v>
+        <v>-381.9009376920151</v>
       </c>
       <c r="P58">
-        <v>-1254.860572332547</v>
+        <v>-1278.537921838486</v>
       </c>
       <c r="Q58">
-        <v>-1223.260572332547</v>
+        <v>-1246.937921838486</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2303509515168958</v>
+        <v>0.234642834110312</v>
       </c>
       <c r="T58">
-        <v>2.854944525730473</v>
+        <v>2.921338584468391</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.01232818521037547</v>
+        <v>0.01211190125931625</v>
       </c>
       <c r="W58">
-        <v>0.2328930139273935</v>
+        <v>0.2329440136830532</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.05360080526250199</v>
+        <v>0.05266044025789673</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6080,22 +6080,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2336745064667745</v>
+        <v>0.2355745064667745</v>
       </c>
       <c r="C59">
-        <v>-1561.62758006937</v>
+        <v>-1746.419734273767</v>
       </c>
       <c r="D59">
-        <v>5432.131281383135</v>
+        <v>5377.745422993695</v>
       </c>
       <c r="E59">
-        <v>6401.529279956882</v>
+        <v>6531.935575771839</v>
       </c>
       <c r="F59">
-        <v>7433.158861452504</v>
+        <v>7563.565157267461</v>
       </c>
       <c r="G59">
         <v>439.4</v>
@@ -6116,37 +6116,37 @@
         <v>92.3</v>
       </c>
       <c r="M59">
-        <v>1752.738859530501</v>
+        <v>1783.488664083668</v>
       </c>
       <c r="N59">
-        <v>-1660.438859530501</v>
+        <v>-1691.188664083668</v>
       </c>
       <c r="O59">
-        <v>-381.9009376920151</v>
+        <v>-388.9733927392436</v>
       </c>
       <c r="P59">
-        <v>-1278.537921838486</v>
+        <v>-1302.215271344424</v>
       </c>
       <c r="Q59">
-        <v>-1246.937921838486</v>
+        <v>-1270.615271344424</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.234642834110312</v>
+        <v>0.2391390920653194</v>
       </c>
       <c r="T59">
-        <v>2.921338584468391</v>
+        <v>2.990894265050971</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.01211190125931625</v>
+        <v>0.01190307537553494</v>
       </c>
       <c r="W59">
-        <v>0.2329440136830532</v>
+        <v>0.2329932548264489</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.05266044025789673</v>
+        <v>0.05175250163276057</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6162,22 +6162,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2355745064667745</v>
+        <v>0.2374745064667745</v>
       </c>
       <c r="C60">
-        <v>-1746.419734273764</v>
+        <v>-1930.13367382307</v>
       </c>
       <c r="D60">
-        <v>5377.745422993696</v>
+        <v>5324.437779259346</v>
       </c>
       <c r="E60">
-        <v>6531.935575771838</v>
+        <v>6662.341871586794</v>
       </c>
       <c r="F60">
-        <v>7563.56515726746</v>
+        <v>7693.971453082416</v>
       </c>
       <c r="G60">
         <v>439.4</v>
@@ -6198,37 +6198,37 @@
         <v>92.3</v>
       </c>
       <c r="M60">
-        <v>1783.488664083667</v>
+        <v>1814.238468636834</v>
       </c>
       <c r="N60">
-        <v>-1691.188664083667</v>
+        <v>-1721.938468636834</v>
       </c>
       <c r="O60">
-        <v>-388.9733927392435</v>
+        <v>-396.0458477864718</v>
       </c>
       <c r="P60">
-        <v>-1302.215271344424</v>
+        <v>-1325.892620850362</v>
       </c>
       <c r="Q60">
-        <v>-1270.615271344424</v>
+        <v>-1294.292620850362</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2391390920653194</v>
+        <v>0.2438546796766686</v>
       </c>
       <c r="T60">
-        <v>2.990894265050971</v>
+        <v>3.06384290566197</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.01190307537553494</v>
+        <v>0.01170132833527163</v>
       </c>
       <c r="W60">
-        <v>0.2329932548264489</v>
+        <v>0.233040826778543</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.05175250163276057</v>
+        <v>0.05087534058813747</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6244,22 +6244,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2374745064667745</v>
+        <v>0.2393745064667745</v>
       </c>
       <c r="C61">
-        <v>-1930.13367382307</v>
+        <v>-2112.801147854328</v>
       </c>
       <c r="D61">
-        <v>5324.437779259346</v>
+        <v>5272.176601043045</v>
       </c>
       <c r="E61">
-        <v>6662.341871586794</v>
+        <v>6792.74816740175</v>
       </c>
       <c r="F61">
-        <v>7693.971453082416</v>
+        <v>7824.377748897372</v>
       </c>
       <c r="G61">
         <v>439.4</v>
@@ -6280,37 +6280,37 @@
         <v>92.3</v>
       </c>
       <c r="M61">
-        <v>1814.238468636834</v>
+        <v>1844.98827319</v>
       </c>
       <c r="N61">
-        <v>-1721.938468636834</v>
+        <v>-1752.68827319</v>
       </c>
       <c r="O61">
-        <v>-396.0458477864718</v>
+        <v>-403.1183028337001</v>
       </c>
       <c r="P61">
-        <v>-1325.892620850362</v>
+        <v>-1349.5699703563</v>
       </c>
       <c r="Q61">
-        <v>-1294.292620850362</v>
+        <v>-1317.969970356301</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2438546796766686</v>
+        <v>0.2488060466685853</v>
       </c>
       <c r="T61">
-        <v>3.06384290566197</v>
+        <v>3.140438978303519</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.01170132833527163</v>
+        <v>0.01150630619635044</v>
       </c>
       <c r="W61">
-        <v>0.233040826778543</v>
+        <v>0.2330868129989006</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.05087534058813747</v>
+        <v>0.0500274182450019</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6326,22 +6326,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2393745064667745</v>
+        <v>0.2412745064667745</v>
       </c>
       <c r="C62">
-        <v>-2112.801147854328</v>
+        <v>-2294.452671106063</v>
       </c>
       <c r="D62">
-        <v>5272.176601043045</v>
+        <v>5220.931373606267</v>
       </c>
       <c r="E62">
-        <v>6792.74816740175</v>
+        <v>6923.154463216707</v>
       </c>
       <c r="F62">
-        <v>7824.377748897372</v>
+        <v>7954.784044712329</v>
       </c>
       <c r="G62">
         <v>439.4</v>
@@ -6362,37 +6362,37 @@
         <v>92.3</v>
       </c>
       <c r="M62">
-        <v>1844.98827319</v>
+        <v>1875.738077743167</v>
       </c>
       <c r="N62">
-        <v>-1752.68827319</v>
+        <v>-1783.438077743167</v>
       </c>
       <c r="O62">
-        <v>-403.1183028337001</v>
+        <v>-410.1907578809285</v>
       </c>
       <c r="P62">
-        <v>-1349.5699703563</v>
+        <v>-1373.247319862239</v>
       </c>
       <c r="Q62">
-        <v>-1317.969970356301</v>
+        <v>-1341.647319862239</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2488060466685853</v>
+        <v>0.2540113299164978</v>
       </c>
       <c r="T62">
-        <v>3.140438978303519</v>
+        <v>3.220963054670277</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.01150630619635044</v>
+        <v>0.01131767822591846</v>
       </c>
       <c r="W62">
-        <v>0.2330868129989006</v>
+        <v>0.2331312914743284</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.0500274182450019</v>
+        <v>0.04920729663442813</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6408,22 +6408,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2412745064667745</v>
+        <v>0.2431745064667745</v>
       </c>
       <c r="C63">
-        <v>-2294.452671106063</v>
+        <v>-2475.11758333216</v>
       </c>
       <c r="D63">
-        <v>5220.931373606267</v>
+        <v>5170.672757195125</v>
       </c>
       <c r="E63">
-        <v>6923.154463216707</v>
+        <v>7053.560759031663</v>
       </c>
       <c r="F63">
-        <v>7954.784044712329</v>
+        <v>8085.190340527285</v>
       </c>
       <c r="G63">
         <v>439.4</v>
@@ -6444,37 +6444,37 @@
         <v>92.3</v>
       </c>
       <c r="M63">
-        <v>1875.738077743167</v>
+        <v>1906.487882296334</v>
       </c>
       <c r="N63">
-        <v>-1783.438077743167</v>
+        <v>-1814.187882296334</v>
       </c>
       <c r="O63">
-        <v>-410.1907578809285</v>
+        <v>-417.2632129281569</v>
       </c>
       <c r="P63">
-        <v>-1373.247319862239</v>
+        <v>-1396.924669368177</v>
       </c>
       <c r="Q63">
-        <v>-1341.647319862239</v>
+        <v>-1365.324669368177</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2540113299164978</v>
+        <v>0.2594905754406162</v>
       </c>
       <c r="T63">
-        <v>3.220963054670277</v>
+        <v>3.305725240319494</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.01131767822591846</v>
+        <v>0.01113513502872623</v>
       </c>
       <c r="W63">
-        <v>0.2331312914743284</v>
+        <v>0.2331743351602264</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.04920729663442813</v>
+        <v>0.04841363055967929</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6490,22 +6490,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2431745064667745</v>
+        <v>0.2450745064667745</v>
       </c>
       <c r="C64">
-        <v>-2475.11758333216</v>
+        <v>-2654.824105316834</v>
       </c>
       <c r="D64">
-        <v>5170.672757195125</v>
+        <v>5121.372531025408</v>
       </c>
       <c r="E64">
-        <v>7053.560759031663</v>
+        <v>7183.967054846619</v>
       </c>
       <c r="F64">
-        <v>8085.190340527285</v>
+        <v>8215.596636342241</v>
       </c>
       <c r="G64">
         <v>439.4</v>
@@ -6526,37 +6526,37 @@
         <v>92.3</v>
       </c>
       <c r="M64">
-        <v>1906.487882296334</v>
+        <v>1937.237686849501</v>
       </c>
       <c r="N64">
-        <v>-1814.187882296334</v>
+        <v>-1844.937686849501</v>
       </c>
       <c r="O64">
-        <v>-417.2632129281569</v>
+        <v>-424.3356679753851</v>
       </c>
       <c r="P64">
-        <v>-1396.924669368177</v>
+        <v>-1420.602018874115</v>
       </c>
       <c r="Q64">
-        <v>-1365.324669368177</v>
+        <v>-1389.002018874115</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2594905754406162</v>
+        <v>0.2652659963984706</v>
       </c>
       <c r="T64">
-        <v>3.305725240319494</v>
+        <v>3.395069165733534</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.01113513502872623</v>
+        <v>0.01095838685366709</v>
       </c>
       <c r="W64">
-        <v>0.2331743351602264</v>
+        <v>0.2332160123799053</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.04841363055967929</v>
+        <v>0.04764516023333509</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6572,22 +6572,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2450745064667745</v>
+        <v>0.2469745064667745</v>
       </c>
       <c r="C65">
-        <v>-2654.824105316834</v>
+        <v>-2833.599391715374</v>
       </c>
       <c r="D65">
-        <v>5121.372531025408</v>
+        <v>5073.003540441825</v>
       </c>
       <c r="E65">
-        <v>7183.967054846619</v>
+        <v>7314.373350661576</v>
       </c>
       <c r="F65">
-        <v>8215.596636342241</v>
+        <v>8346.002932157198</v>
       </c>
       <c r="G65">
         <v>439.4</v>
@@ -6608,37 +6608,37 @@
         <v>92.3</v>
       </c>
       <c r="M65">
-        <v>1937.237686849501</v>
+        <v>1967.987491402668</v>
       </c>
       <c r="N65">
-        <v>-1844.937686849501</v>
+        <v>-1875.687491402668</v>
       </c>
       <c r="O65">
-        <v>-424.3356679753851</v>
+        <v>-431.4081230226136</v>
       </c>
       <c r="P65">
-        <v>-1420.602018874115</v>
+        <v>-1444.279368380054</v>
       </c>
       <c r="Q65">
-        <v>-1389.002018874115</v>
+        <v>-1412.679368380054</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2652659963984706</v>
+        <v>0.2713622740762059</v>
       </c>
       <c r="T65">
-        <v>3.395069165733534</v>
+        <v>3.489376642559466</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.01095838685366709</v>
+        <v>0.01078716205907853</v>
       </c>
       <c r="W65">
-        <v>0.2332160123799053</v>
+        <v>0.2332563871864693</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.04764516023333509</v>
+        <v>0.04690070460468931</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6654,22 +6654,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2469745064667745</v>
+        <v>0.2488745064667745</v>
       </c>
       <c r="C66">
-        <v>-2833.599391715374</v>
+        <v>-3011.469580928569</v>
       </c>
       <c r="D66">
-        <v>5073.003540441825</v>
+        <v>5025.539647043584</v>
       </c>
       <c r="E66">
-        <v>7314.373350661576</v>
+        <v>7444.779646476532</v>
       </c>
       <c r="F66">
-        <v>8346.002932157198</v>
+        <v>8476.409227972154</v>
       </c>
       <c r="G66">
         <v>439.4</v>
@@ -6690,37 +6690,37 @@
         <v>92.3</v>
       </c>
       <c r="M66">
-        <v>1967.987491402668</v>
+        <v>1998.737295955834</v>
       </c>
       <c r="N66">
-        <v>-1875.687491402668</v>
+        <v>-1906.437295955834</v>
       </c>
       <c r="O66">
-        <v>-431.4081230226136</v>
+        <v>-438.4805780698418</v>
       </c>
       <c r="P66">
-        <v>-1444.279368380054</v>
+        <v>-1467.956717885992</v>
       </c>
       <c r="Q66">
-        <v>-1412.679368380054</v>
+        <v>-1436.356717885992</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2713622740762059</v>
+        <v>0.2778069104783832</v>
       </c>
       <c r="T66">
-        <v>3.489376642559466</v>
+        <v>3.589073118061165</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.01078716205907853</v>
+        <v>0.0106212057197081</v>
       </c>
       <c r="W66">
-        <v>0.2332563871864693</v>
+        <v>0.2332955196912928</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.04690070460468931</v>
+        <v>0.0461791553030787</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6736,22 +6736,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2488745064667745</v>
+        <v>0.2507745064667745</v>
       </c>
       <c r="C67">
-        <v>-3011.469580928569</v>
+        <v>-3188.459842203302</v>
       </c>
       <c r="D67">
-        <v>5025.539647043584</v>
+        <v>4978.955681583809</v>
       </c>
       <c r="E67">
-        <v>7444.779646476532</v>
+        <v>7575.185942291489</v>
       </c>
       <c r="F67">
-        <v>8476.409227972154</v>
+        <v>8606.815523787111</v>
       </c>
       <c r="G67">
         <v>439.4</v>
@@ -6772,37 +6772,37 @@
         <v>92.3</v>
       </c>
       <c r="M67">
-        <v>1998.737295955834</v>
+        <v>2029.487100509001</v>
       </c>
       <c r="N67">
-        <v>-1906.437295955834</v>
+        <v>-1937.187100509001</v>
       </c>
       <c r="O67">
-        <v>-438.4805780698418</v>
+        <v>-445.5530331170702</v>
       </c>
       <c r="P67">
-        <v>-1467.956717885992</v>
+        <v>-1491.634067391931</v>
       </c>
       <c r="Q67">
-        <v>-1436.356717885992</v>
+        <v>-1460.034067391931</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2778069104783832</v>
+        <v>0.2846306431395122</v>
       </c>
       <c r="T67">
-        <v>3.589073118061165</v>
+        <v>3.694634092121788</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.0106212057197081</v>
+        <v>0.01046027836031858</v>
       </c>
       <c r="W67">
-        <v>0.2332955196912928</v>
+        <v>0.2333334663626369</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.0461791553030787</v>
+        <v>0.04547947113181994</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6818,22 +6818,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2507745064667745</v>
+        <v>0.2526745064667745</v>
       </c>
       <c r="C68">
-        <v>-3188.459842203302</v>
+        <v>-3364.594420137585</v>
       </c>
       <c r="D68">
-        <v>4978.955681583809</v>
+        <v>4933.227399464481</v>
       </c>
       <c r="E68">
-        <v>7575.185942291489</v>
+        <v>7705.592238106444</v>
       </c>
       <c r="F68">
-        <v>8606.815523787111</v>
+        <v>8737.221819602066</v>
       </c>
       <c r="G68">
         <v>439.4</v>
@@ -6854,37 +6854,37 @@
         <v>92.3</v>
       </c>
       <c r="M68">
-        <v>2029.487100509001</v>
+        <v>2060.236905062167</v>
       </c>
       <c r="N68">
-        <v>-1937.187100509001</v>
+        <v>-1967.936905062167</v>
       </c>
       <c r="O68">
-        <v>-445.5530331170702</v>
+        <v>-452.6254881642985</v>
       </c>
       <c r="P68">
-        <v>-1491.634067391931</v>
+        <v>-1515.311416897869</v>
       </c>
       <c r="Q68">
-        <v>-1460.034067391931</v>
+        <v>-1483.711416897869</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2846306431395122</v>
+        <v>0.2918679353558611</v>
       </c>
       <c r="T68">
-        <v>3.694634092121788</v>
+        <v>3.806592700973964</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.01046027836031858</v>
+        <v>0.01030415480270189</v>
       </c>
       <c r="W68">
-        <v>0.2333334663626369</v>
+        <v>0.2333702802975229</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.04547947113181994</v>
+        <v>0.04480067305522561</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6900,22 +6900,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2526745064667745</v>
+        <v>0.2545745064667745</v>
       </c>
       <c r="C69">
-        <v>-3364.594420137585</v>
+        <v>-3539.896676755468</v>
       </c>
       <c r="D69">
-        <v>4933.227399464481</v>
+        <v>4888.331438661555</v>
       </c>
       <c r="E69">
-        <v>7705.592238106444</v>
+        <v>7835.998533921401</v>
       </c>
       <c r="F69">
-        <v>8737.221819602066</v>
+        <v>8867.628115417023</v>
       </c>
       <c r="G69">
         <v>439.4</v>
@@ -6936,37 +6936,37 @@
         <v>92.3</v>
       </c>
       <c r="M69">
-        <v>2060.236905062167</v>
+        <v>2090.986709615334</v>
       </c>
       <c r="N69">
-        <v>-1967.936905062167</v>
+        <v>-1998.686709615334</v>
       </c>
       <c r="O69">
-        <v>-452.6254881642985</v>
+        <v>-459.6979432115268</v>
       </c>
       <c r="P69">
-        <v>-1515.311416897869</v>
+        <v>-1538.988766403807</v>
       </c>
       <c r="Q69">
-        <v>-1483.711416897869</v>
+        <v>-1507.388766403807</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2918679353558611</v>
+        <v>0.2995575583357317</v>
       </c>
       <c r="T69">
-        <v>3.806592700973964</v>
+        <v>3.9255487228794</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.01030415480270189</v>
+        <v>0.01015262311442686</v>
       </c>
       <c r="W69">
-        <v>0.2333702802975229</v>
+        <v>0.2334060114696181</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.04480067305522561</v>
+        <v>0.04414183962794282</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6982,22 +6982,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2545745064667745</v>
+        <v>0.2564745064667746</v>
       </c>
       <c r="C70">
-        <v>-3539.896676755468</v>
+        <v>-3714.389131305164</v>
       </c>
       <c r="D70">
-        <v>4888.331438661555</v>
+        <v>4844.245279926816</v>
       </c>
       <c r="E70">
-        <v>7835.998533921401</v>
+        <v>7966.404829736358</v>
       </c>
       <c r="F70">
-        <v>8867.628115417023</v>
+        <v>8998.03441123198</v>
       </c>
       <c r="G70">
         <v>439.4</v>
@@ -7018,37 +7018,37 @@
         <v>92.3</v>
       </c>
       <c r="M70">
-        <v>2090.986709615334</v>
+        <v>2121.736514168501</v>
       </c>
       <c r="N70">
-        <v>-1998.686709615334</v>
+        <v>-2029.436514168501</v>
       </c>
       <c r="O70">
-        <v>-459.6979432115268</v>
+        <v>-466.7703982587552</v>
       </c>
       <c r="P70">
-        <v>-1538.988766403807</v>
+        <v>-1562.666115909746</v>
       </c>
       <c r="Q70">
-        <v>-1507.388766403807</v>
+        <v>-1531.066115909746</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2995575583357317</v>
+        <v>0.3077432860239812</v>
       </c>
       <c r="T70">
-        <v>3.9255487228794</v>
+        <v>4.052179326843253</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.01015262311442686</v>
+        <v>0.01000548364900038</v>
       </c>
       <c r="W70">
-        <v>0.2334060114696181</v>
+        <v>0.2334407069555657</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.04414183962794282</v>
+        <v>0.04350210282174072</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7064,22 +7064,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2564745064667746</v>
+        <v>0.2583745064667745</v>
       </c>
       <c r="C71">
-        <v>-3714.389131305164</v>
+        <v>-3888.093497922883</v>
       </c>
       <c r="D71">
-        <v>4844.245279926816</v>
+        <v>4800.947209124052</v>
       </c>
       <c r="E71">
-        <v>7966.404829736358</v>
+        <v>8096.811125551313</v>
       </c>
       <c r="F71">
-        <v>8998.03441123198</v>
+        <v>9128.440707046935</v>
       </c>
       <c r="G71">
         <v>439.4</v>
@@ -7100,37 +7100,37 @@
         <v>92.3</v>
       </c>
       <c r="M71">
-        <v>2121.736514168501</v>
+        <v>2152.486318721667</v>
       </c>
       <c r="N71">
-        <v>-2029.436514168501</v>
+        <v>-2060.186318721667</v>
       </c>
       <c r="O71">
-        <v>-466.7703982587552</v>
+        <v>-473.8428533059835</v>
       </c>
       <c r="P71">
-        <v>-1562.666115909746</v>
+        <v>-1586.343465415684</v>
       </c>
       <c r="Q71">
-        <v>-1531.066115909746</v>
+        <v>-1554.743465415684</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3077432860239812</v>
+        <v>0.3164747288914472</v>
       </c>
       <c r="T71">
-        <v>4.052179326843253</v>
+        <v>4.18725197107136</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01000548364900038</v>
+        <v>0.009862548168300376</v>
       </c>
       <c r="W71">
-        <v>0.2334407069555657</v>
+        <v>0.2334744111419148</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.04350210282174072</v>
+        <v>0.04288064421000171</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7146,22 +7146,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2583745064667745</v>
+        <v>0.2602745064667745</v>
       </c>
       <c r="C72">
-        <v>-3888.093497922883</v>
+        <v>-4061.030721294718</v>
       </c>
       <c r="D72">
-        <v>4800.947209124052</v>
+        <v>4758.416281567174</v>
       </c>
       <c r="E72">
-        <v>8096.811125551313</v>
+        <v>8227.217421366269</v>
       </c>
       <c r="F72">
-        <v>9128.440707046935</v>
+        <v>9258.847002861892</v>
       </c>
       <c r="G72">
         <v>439.4</v>
@@ -7182,37 +7182,37 @@
         <v>92.3</v>
       </c>
       <c r="M72">
-        <v>2152.486318721667</v>
+        <v>2183.236123274834</v>
       </c>
       <c r="N72">
-        <v>-2060.186318721667</v>
+        <v>-2090.936123274834</v>
       </c>
       <c r="O72">
-        <v>-473.8428533059835</v>
+        <v>-480.9153083532119</v>
       </c>
       <c r="P72">
-        <v>-1586.343465415684</v>
+        <v>-1610.020814921622</v>
       </c>
       <c r="Q72">
-        <v>-1554.743465415684</v>
+        <v>-1578.420814921622</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3164747288914472</v>
+        <v>0.3258083402325316</v>
       </c>
       <c r="T72">
-        <v>4.18725197107136</v>
+        <v>4.331639970073821</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.009862548168300376</v>
+        <v>0.009723639039169384</v>
       </c>
       <c r="W72">
-        <v>0.2334744111419148</v>
+        <v>0.2335071659145639</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.04288064421000171</v>
+        <v>0.04227669147464963</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7228,22 +7228,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2602745064667745</v>
+        <v>0.2621745064667745</v>
       </c>
       <c r="C73">
-        <v>-4061.030721294716</v>
+        <v>-4233.221010439618</v>
       </c>
       <c r="D73">
-        <v>4758.416281567174</v>
+        <v>4716.63228823723</v>
       </c>
       <c r="E73">
-        <v>8227.217421366269</v>
+        <v>8357.623717181224</v>
       </c>
       <c r="F73">
-        <v>9258.84700286189</v>
+        <v>9389.253298676847</v>
       </c>
       <c r="G73">
         <v>439.4</v>
@@ -7264,37 +7264,37 @@
         <v>92.3</v>
       </c>
       <c r="M73">
-        <v>2183.236123274834</v>
+        <v>2213.985927828001</v>
       </c>
       <c r="N73">
-        <v>-2090.936123274834</v>
+        <v>-2121.685927828</v>
       </c>
       <c r="O73">
-        <v>-480.9153083532118</v>
+        <v>-487.9877634004401</v>
       </c>
       <c r="P73">
-        <v>-1610.020814921622</v>
+        <v>-1633.69816442756</v>
       </c>
       <c r="Q73">
-        <v>-1578.420814921622</v>
+        <v>-1602.09816442756</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3258083402325315</v>
+        <v>0.3358086380979791</v>
       </c>
       <c r="T73">
-        <v>4.33163997007382</v>
+        <v>4.486341397576457</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.009723639039169386</v>
+        <v>0.0095885884969587</v>
       </c>
       <c r="W73">
-        <v>0.2335071659145639</v>
+        <v>0.2335390108324172</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.04227669147464963</v>
+        <v>0.0416895152041683</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7310,22 +7310,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2621745064667745</v>
+        <v>0.2640745064667745</v>
       </c>
       <c r="C74">
-        <v>-4233.221010439618</v>
+        <v>-4404.683870727964</v>
       </c>
       <c r="D74">
-        <v>4716.63228823723</v>
+        <v>4675.575723763839</v>
       </c>
       <c r="E74">
-        <v>8357.623717181224</v>
+        <v>8488.03001299618</v>
       </c>
       <c r="F74">
-        <v>9389.253298676847</v>
+        <v>9519.659594491803</v>
       </c>
       <c r="G74">
         <v>439.4</v>
@@ -7346,37 +7346,37 @@
         <v>92.3</v>
       </c>
       <c r="M74">
-        <v>2213.985927828001</v>
+        <v>2244.735732381167</v>
       </c>
       <c r="N74">
-        <v>-2121.685927828</v>
+        <v>-2152.435732381167</v>
       </c>
       <c r="O74">
-        <v>-487.9877634004401</v>
+        <v>-495.0602184476684</v>
       </c>
       <c r="P74">
-        <v>-1633.69816442756</v>
+        <v>-1657.375513933498</v>
       </c>
       <c r="Q74">
-        <v>-1602.09816442756</v>
+        <v>-1625.775513933499</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3358086380979791</v>
+        <v>0.3465496987682746</v>
       </c>
       <c r="T74">
-        <v>4.486341397576457</v>
+        <v>4.652502190079288</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0095885884969587</v>
+        <v>0.009457237969603103</v>
       </c>
       <c r="W74">
-        <v>0.2335390108324172</v>
+        <v>0.2335699832867676</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.0416895152041683</v>
+        <v>0.0411184259547962</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7392,22 +7392,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2640745064667745</v>
+        <v>0.2659745064667745</v>
       </c>
       <c r="C75">
-        <v>-4404.683870727964</v>
+        <v>-4575.438134242314</v>
       </c>
       <c r="D75">
-        <v>4675.575723763839</v>
+        <v>4635.227756064446</v>
       </c>
       <c r="E75">
-        <v>8488.03001299618</v>
+        <v>8618.436308811139</v>
       </c>
       <c r="F75">
-        <v>9519.659594491803</v>
+        <v>9650.06589030676</v>
       </c>
       <c r="G75">
         <v>439.4</v>
@@ -7428,37 +7428,37 @@
         <v>92.3</v>
       </c>
       <c r="M75">
-        <v>2244.735732381167</v>
+        <v>2275.485536934334</v>
       </c>
       <c r="N75">
-        <v>-2152.435732381167</v>
+        <v>-2183.185536934334</v>
       </c>
       <c r="O75">
-        <v>-495.0602184476684</v>
+        <v>-502.1326734948968</v>
       </c>
       <c r="P75">
-        <v>-1657.375513933498</v>
+        <v>-1681.052863439437</v>
       </c>
       <c r="Q75">
-        <v>-1625.775513933499</v>
+        <v>-1649.452863439437</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3465496987682746</v>
+        <v>0.3581169948747466</v>
       </c>
       <c r="T75">
-        <v>4.652502190079288</v>
+        <v>4.831444582005414</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.009457237969603103</v>
+        <v>0.009329437456500356</v>
       </c>
       <c r="W75">
-        <v>0.2335699832867676</v>
+        <v>0.2336001186477572</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.0411184259547962</v>
+        <v>0.04056277155000165</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7474,22 +7474,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2659745064667745</v>
+        <v>0.2678745064667745</v>
       </c>
       <c r="C76">
-        <v>-4575.438134242314</v>
+        <v>-4745.501988579594</v>
       </c>
       <c r="D76">
-        <v>4635.227756064446</v>
+        <v>4595.570197542122</v>
       </c>
       <c r="E76">
-        <v>8618.436308811139</v>
+        <v>8748.842604626094</v>
       </c>
       <c r="F76">
-        <v>9650.06589030676</v>
+        <v>9780.472186121715</v>
       </c>
       <c r="G76">
         <v>439.4</v>
@@ -7510,37 +7510,37 @@
         <v>92.3</v>
       </c>
       <c r="M76">
-        <v>2275.485536934334</v>
+        <v>2306.235341487501</v>
       </c>
       <c r="N76">
-        <v>-2183.185536934334</v>
+        <v>-2213.9353414875</v>
       </c>
       <c r="O76">
-        <v>-502.1326734948968</v>
+        <v>-509.2051285421251</v>
       </c>
       <c r="P76">
-        <v>-1681.052863439437</v>
+        <v>-1704.730212945375</v>
       </c>
       <c r="Q76">
-        <v>-1649.452863439437</v>
+        <v>-1673.130212945375</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3581169948747466</v>
+        <v>0.3706096746697365</v>
       </c>
       <c r="T76">
-        <v>4.831444582005414</v>
+        <v>5.024702365285632</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.009329437456500356</v>
+        <v>0.009205044957080352</v>
       </c>
       <c r="W76">
-        <v>0.2336001186477572</v>
+        <v>0.2336294503991205</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.04056277155000165</v>
+        <v>0.04002193459600156</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7556,22 +7556,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2678745064667745</v>
+        <v>0.2697745064667745</v>
       </c>
       <c r="C77">
-        <v>-4745.501988579594</v>
+        <v>-4914.893004187316</v>
       </c>
       <c r="D77">
-        <v>4595.570197542122</v>
+        <v>4556.585477749356</v>
       </c>
       <c r="E77">
-        <v>8748.842604626094</v>
+        <v>8879.248900441049</v>
       </c>
       <c r="F77">
-        <v>9780.472186121715</v>
+        <v>9910.878481936672</v>
       </c>
       <c r="G77">
         <v>439.4</v>
@@ -7592,37 +7592,37 @@
         <v>92.3</v>
       </c>
       <c r="M77">
-        <v>2306.235341487501</v>
+        <v>2336.985146040667</v>
       </c>
       <c r="N77">
-        <v>-2213.9353414875</v>
+        <v>-2244.685146040667</v>
       </c>
       <c r="O77">
-        <v>-509.2051285421251</v>
+        <v>-516.2775835893534</v>
       </c>
       <c r="P77">
-        <v>-1704.730212945375</v>
+        <v>-1728.407562451313</v>
       </c>
       <c r="Q77">
-        <v>-1673.130212945375</v>
+        <v>-1696.807562451314</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3706096746697365</v>
+        <v>0.3841434111143089</v>
       </c>
       <c r="T77">
-        <v>5.024702365285632</v>
+        <v>5.2340649638392</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.009205044957080352</v>
+        <v>0.009083925944487189</v>
       </c>
       <c r="W77">
-        <v>0.2336294503991205</v>
+        <v>0.2336580102622899</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.04002193459600156</v>
+        <v>0.03949533019342266</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7638,22 +7638,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2697745064667745</v>
+        <v>0.2716745064667745</v>
       </c>
       <c r="C78">
-        <v>-4914.893004187316</v>
+        <v>-5083.628160320103</v>
       </c>
       <c r="D78">
-        <v>4556.585477749356</v>
+        <v>4518.256617431526</v>
       </c>
       <c r="E78">
-        <v>8879.248900441049</v>
+        <v>9009.655196256008</v>
       </c>
       <c r="F78">
-        <v>9910.878481936672</v>
+        <v>10041.28477775163</v>
       </c>
       <c r="G78">
         <v>439.4</v>
@@ -7674,37 +7674,37 @@
         <v>92.3</v>
       </c>
       <c r="M78">
-        <v>2336.985146040667</v>
+        <v>2367.734950593834</v>
       </c>
       <c r="N78">
-        <v>-2244.685146040667</v>
+        <v>-2275.434950593834</v>
       </c>
       <c r="O78">
-        <v>-516.2775835893534</v>
+        <v>-523.3500386365819</v>
       </c>
       <c r="P78">
-        <v>-1728.407562451313</v>
+        <v>-1752.084911957252</v>
       </c>
       <c r="Q78">
-        <v>-1696.807562451314</v>
+        <v>-1720.484911957252</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3841434111143089</v>
+        <v>0.3988539942062355</v>
       </c>
       <c r="T78">
-        <v>5.2340649638392</v>
+        <v>5.461633005745252</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.009083925944487189</v>
+        <v>0.008965952880273069</v>
       </c>
       <c r="W78">
-        <v>0.2336580102622899</v>
+        <v>0.2336858283108316</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.03949533019342266</v>
+        <v>0.03898240382727425</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7720,22 +7720,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2716745064667745</v>
+        <v>0.2735745064667745</v>
       </c>
       <c r="C79">
-        <v>-5083.628160320103</v>
+        <v>-5251.723869697117</v>
       </c>
       <c r="D79">
-        <v>4518.256617431526</v>
+        <v>4480.567203869467</v>
       </c>
       <c r="E79">
-        <v>9009.655196256008</v>
+        <v>9140.061492070963</v>
       </c>
       <c r="F79">
-        <v>10041.28477775163</v>
+        <v>10171.69107356658</v>
       </c>
       <c r="G79">
         <v>439.4</v>
@@ -7756,37 +7756,37 @@
         <v>92.3</v>
       </c>
       <c r="M79">
-        <v>2367.734950593834</v>
+        <v>2398.484755147001</v>
       </c>
       <c r="N79">
-        <v>-2275.434950593834</v>
+        <v>-2306.184755147</v>
       </c>
       <c r="O79">
-        <v>-523.3500386365819</v>
+        <v>-530.4224936838101</v>
       </c>
       <c r="P79">
-        <v>-1752.084911957252</v>
+        <v>-1775.76226146319</v>
       </c>
       <c r="Q79">
-        <v>-1720.484911957252</v>
+        <v>-1744.162261463191</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3988539942062355</v>
+        <v>0.4149019030337916</v>
       </c>
       <c r="T79">
-        <v>5.461633005745252</v>
+        <v>5.709889051460945</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.008965952880273069</v>
+        <v>0.008851004766423415</v>
       </c>
       <c r="W79">
-        <v>0.2336858283108316</v>
+        <v>0.2337129330760774</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.03898240382727425</v>
+        <v>0.03848262941923231</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7802,22 +7802,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2735745064667745</v>
+        <v>0.2754745064667745</v>
       </c>
       <c r="C80">
-        <v>-5251.723869697117</v>
+        <v>-5419.196001935602</v>
       </c>
       <c r="D80">
-        <v>4480.567203869467</v>
+        <v>4443.50136744594</v>
       </c>
       <c r="E80">
-        <v>9140.061492070963</v>
+        <v>9270.467787885918</v>
       </c>
       <c r="F80">
-        <v>10171.69107356658</v>
+        <v>10302.09736938154</v>
       </c>
       <c r="G80">
         <v>439.4</v>
@@ -7838,37 +7838,37 @@
         <v>92.3</v>
       </c>
       <c r="M80">
-        <v>2398.484755147001</v>
+        <v>2429.234559700168</v>
       </c>
       <c r="N80">
-        <v>-2306.184755147</v>
+        <v>-2336.934559700167</v>
       </c>
       <c r="O80">
-        <v>-530.4224936838101</v>
+        <v>-537.4949487310386</v>
       </c>
       <c r="P80">
-        <v>-1775.76226146319</v>
+        <v>-1799.439610969129</v>
       </c>
       <c r="Q80">
-        <v>-1744.162261463191</v>
+        <v>-1767.839610969129</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4149019030337916</v>
+        <v>0.4324781841306388</v>
       </c>
       <c r="T80">
-        <v>5.709889051460945</v>
+        <v>5.981788530101943</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.008851004766423415</v>
+        <v>0.008738966731405395</v>
       </c>
       <c r="W80">
-        <v>0.2337129330760774</v>
+        <v>0.2337393516447346</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.03848262941923231</v>
+        <v>0.03799550752784964</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7884,22 +7884,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2754745064667745</v>
+        <v>0.2773745064667745</v>
       </c>
       <c r="C81">
-        <v>-5419.196001935602</v>
+        <v>-5586.059905830828</v>
       </c>
       <c r="D81">
-        <v>4443.50136744594</v>
+        <v>4407.043759365671</v>
       </c>
       <c r="E81">
-        <v>9270.467787885918</v>
+        <v>9400.874083700877</v>
       </c>
       <c r="F81">
-        <v>10302.09736938154</v>
+        <v>10432.5036651965</v>
       </c>
       <c r="G81">
         <v>439.4</v>
@@ -7920,37 +7920,37 @@
         <v>92.3</v>
       </c>
       <c r="M81">
-        <v>2429.234559700168</v>
+        <v>2459.984364253334</v>
       </c>
       <c r="N81">
-        <v>-2336.934559700167</v>
+        <v>-2367.684364253334</v>
       </c>
       <c r="O81">
-        <v>-537.4949487310386</v>
+        <v>-544.5674037782668</v>
       </c>
       <c r="P81">
-        <v>-1799.439610969129</v>
+        <v>-1823.116960475067</v>
       </c>
       <c r="Q81">
-        <v>-1767.839610969129</v>
+        <v>-1791.516960475067</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4324781841306388</v>
+        <v>0.4518120933371708</v>
       </c>
       <c r="T81">
-        <v>5.981788530101943</v>
+        <v>6.28087795660704</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.008738966731405395</v>
+        <v>0.008629729647262829</v>
       </c>
       <c r="W81">
-        <v>0.2337393516447346</v>
+        <v>0.2337651097491754</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.03799550752784964</v>
+        <v>0.03752056368375145</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7966,22 +7966,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2773745064667745</v>
+        <v>0.2792745064667745</v>
       </c>
       <c r="C82">
-        <v>-5586.059905830828</v>
+        <v>-5752.330430548163</v>
       </c>
       <c r="D82">
-        <v>4407.043759365671</v>
+        <v>4371.179530463291</v>
       </c>
       <c r="E82">
-        <v>9400.874083700877</v>
+        <v>9531.280379515832</v>
       </c>
       <c r="F82">
-        <v>10432.5036651965</v>
+        <v>10562.90996101145</v>
       </c>
       <c r="G82">
         <v>439.4</v>
@@ -8002,37 +8002,37 @@
         <v>92.3</v>
       </c>
       <c r="M82">
-        <v>2459.984364253334</v>
+        <v>2490.734168806501</v>
       </c>
       <c r="N82">
-        <v>-2367.684364253334</v>
+        <v>-2398.434168806501</v>
       </c>
       <c r="O82">
-        <v>-544.5674037782668</v>
+        <v>-551.6398588254951</v>
       </c>
       <c r="P82">
-        <v>-1823.116960475067</v>
+        <v>-1846.794309981005</v>
       </c>
       <c r="Q82">
-        <v>-1791.516960475067</v>
+        <v>-1815.194309981006</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4518120933371708</v>
+        <v>0.4731811508812324</v>
       </c>
       <c r="T82">
-        <v>6.28087795660704</v>
+        <v>6.61145048063899</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.008629729647262829</v>
+        <v>0.008523189775074399</v>
       </c>
       <c r="W82">
-        <v>0.2337651097491754</v>
+        <v>0.2337902318510375</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.03752056368375145</v>
+        <v>0.03705734684814965</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8048,22 +8048,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2792745064667745</v>
+        <v>0.2811745064667745</v>
       </c>
       <c r="C83">
-        <v>-5752.330430548163</v>
+        <v>-5918.021945788753</v>
       </c>
       <c r="D83">
-        <v>4371.179530463291</v>
+        <v>4335.894311037658</v>
       </c>
       <c r="E83">
-        <v>9531.280379515832</v>
+        <v>9661.686675330788</v>
       </c>
       <c r="F83">
-        <v>10562.90996101145</v>
+        <v>10693.31625682641</v>
       </c>
       <c r="G83">
         <v>439.4</v>
@@ -8084,37 +8084,37 @@
         <v>92.3</v>
       </c>
       <c r="M83">
-        <v>2490.734168806501</v>
+        <v>2521.483973359668</v>
       </c>
       <c r="N83">
-        <v>-2398.434168806501</v>
+        <v>-2429.183973359668</v>
       </c>
       <c r="O83">
-        <v>-551.6398588254951</v>
+        <v>-558.7123138727236</v>
       </c>
       <c r="P83">
-        <v>-1846.794309981005</v>
+        <v>-1870.471659486944</v>
       </c>
       <c r="Q83">
-        <v>-1815.194309981006</v>
+        <v>-1838.871659486944</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4731811508812324</v>
+        <v>0.496924548152412</v>
       </c>
       <c r="T83">
-        <v>6.61145048063899</v>
+        <v>6.978753285118935</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.008523189775074399</v>
+        <v>0.008419248436353978</v>
       </c>
       <c r="W83">
-        <v>0.2337902318510375</v>
+        <v>0.2338147412187077</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.03705734684814965</v>
+        <v>0.03660542798414779</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8130,22 +8130,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2811745064667745</v>
+        <v>0.2830745064667745</v>
       </c>
       <c r="C84">
-        <v>-5918.021945788753</v>
+        <v>-6083.148360986298</v>
       </c>
       <c r="D84">
-        <v>4335.894311037658</v>
+        <v>4301.174191655068</v>
       </c>
       <c r="E84">
-        <v>9661.686675330788</v>
+        <v>9792.092971145743</v>
       </c>
       <c r="F84">
-        <v>10693.31625682641</v>
+        <v>10823.72255264137</v>
       </c>
       <c r="G84">
         <v>439.4</v>
@@ -8166,37 +8166,37 @@
         <v>92.3</v>
       </c>
       <c r="M84">
-        <v>2521.483973359668</v>
+        <v>2552.233777912834</v>
       </c>
       <c r="N84">
-        <v>-2429.183973359668</v>
+        <v>-2459.933777912834</v>
       </c>
       <c r="O84">
-        <v>-558.7123138727236</v>
+        <v>-565.7847689199518</v>
       </c>
       <c r="P84">
-        <v>-1870.471659486944</v>
+        <v>-1894.149008992882</v>
       </c>
       <c r="Q84">
-        <v>-1838.871659486944</v>
+        <v>-1862.549008992882</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.496924548152412</v>
+        <v>0.5234612862790244</v>
       </c>
       <c r="T84">
-        <v>6.978753285118935</v>
+        <v>7.389268184243578</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.008419248436353978</v>
+        <v>0.008317811708205137</v>
       </c>
       <c r="W84">
-        <v>0.2338147412187077</v>
+        <v>0.2338386599992053</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.03660542798414779</v>
+        <v>0.03616439873132671</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8212,22 +8212,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2830745064667745</v>
+        <v>0.2849745064667745</v>
       </c>
       <c r="C85">
-        <v>-6083.148360986298</v>
+        <v>-6247.723143588872</v>
       </c>
       <c r="D85">
-        <v>4301.174191655068</v>
+        <v>4267.005704867452</v>
       </c>
       <c r="E85">
-        <v>9792.092971145743</v>
+        <v>9922.499266960702</v>
       </c>
       <c r="F85">
-        <v>10823.72255264137</v>
+        <v>10954.12884845632</v>
       </c>
       <c r="G85">
         <v>439.4</v>
@@ -8248,37 +8248,37 @@
         <v>92.3</v>
       </c>
       <c r="M85">
-        <v>2552.233777912834</v>
+        <v>2582.983582466001</v>
       </c>
       <c r="N85">
-        <v>-2459.933777912834</v>
+        <v>-2490.683582466001</v>
       </c>
       <c r="O85">
-        <v>-565.7847689199518</v>
+        <v>-572.8572239671802</v>
       </c>
       <c r="P85">
-        <v>-1894.149008992882</v>
+        <v>-1917.82635849882</v>
       </c>
       <c r="Q85">
-        <v>-1862.549008992882</v>
+        <v>-1886.22635849882</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5234612862790244</v>
+        <v>0.5533151166714636</v>
       </c>
       <c r="T85">
-        <v>7.389268184243578</v>
+        <v>7.851097445758803</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.008317811708205137</v>
+        <v>0.008218790140250313</v>
       </c>
       <c r="W85">
-        <v>0.2338386599992053</v>
+        <v>0.233862009284929</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.03616439873132671</v>
+        <v>0.0357338701750014</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8294,22 +8294,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2849745064667745</v>
+        <v>0.2868745064667745</v>
       </c>
       <c r="C86">
-        <v>-6247.72314358887</v>
+        <v>-6411.75933647619</v>
       </c>
       <c r="D86">
-        <v>4267.005704867452</v>
+        <v>4233.375807795089</v>
       </c>
       <c r="E86">
-        <v>9922.499266960698</v>
+        <v>10052.90556277566</v>
       </c>
       <c r="F86">
-        <v>10954.12884845632</v>
+        <v>11084.53514427128</v>
       </c>
       <c r="G86">
         <v>439.4</v>
@@ -8330,37 +8330,37 @@
         <v>92.3</v>
       </c>
       <c r="M86">
-        <v>2582.983582466001</v>
+        <v>2613.733387019167</v>
       </c>
       <c r="N86">
-        <v>-2490.683582466001</v>
+        <v>-2521.433387019167</v>
       </c>
       <c r="O86">
-        <v>-572.8572239671802</v>
+        <v>-579.9296790144085</v>
       </c>
       <c r="P86">
-        <v>-1917.82635849882</v>
+        <v>-1941.503708004759</v>
       </c>
       <c r="Q86">
-        <v>-1886.22635849882</v>
+        <v>-1909.903708004759</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5533151166714633</v>
+        <v>0.5871494577828942</v>
       </c>
       <c r="T86">
-        <v>7.851097445758798</v>
+        <v>8.374503942142718</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.008218790140250313</v>
+        <v>0.008122098491541488</v>
       </c>
       <c r="W86">
-        <v>0.233862009284929</v>
+        <v>0.2338848091756945</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.0357338701750014</v>
+        <v>0.03531347170235433</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8376,22 +8376,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2868745064667745</v>
+        <v>0.2887745064667745</v>
       </c>
       <c r="C87">
-        <v>-6411.75933647619</v>
+        <v>-6575.269574559717</v>
       </c>
       <c r="D87">
-        <v>4233.375807795089</v>
+        <v>4200.271865526517</v>
       </c>
       <c r="E87">
-        <v>10052.90556277566</v>
+        <v>10183.31185859061</v>
       </c>
       <c r="F87">
-        <v>11084.53514427128</v>
+        <v>11214.94144008623</v>
       </c>
       <c r="G87">
         <v>439.4</v>
@@ -8412,37 +8412,37 @@
         <v>92.3</v>
       </c>
       <c r="M87">
-        <v>2613.733387019167</v>
+        <v>2644.483191572334</v>
       </c>
       <c r="N87">
-        <v>-2521.433387019167</v>
+        <v>-2552.183191572334</v>
       </c>
       <c r="O87">
-        <v>-579.9296790144085</v>
+        <v>-587.0021340616368</v>
       </c>
       <c r="P87">
-        <v>-1941.503708004759</v>
+        <v>-1965.181057510697</v>
       </c>
       <c r="Q87">
-        <v>-1909.903708004759</v>
+        <v>-1933.581057510697</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5871494577828942</v>
+        <v>0.6258172761959581</v>
       </c>
       <c r="T87">
-        <v>8.374503942142718</v>
+        <v>8.972682795152913</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.008122098491541488</v>
+        <v>0.008027655485825888</v>
       </c>
       <c r="W87">
-        <v>0.2338848091756945</v>
+        <v>0.2339070788364423</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.03531347170235433</v>
+        <v>0.03490284993837345</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8458,22 +8458,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2887745064667745</v>
+        <v>0.2906745064667745</v>
       </c>
       <c r="C88">
-        <v>-6575.269574559717</v>
+        <v>-6738.266100609942</v>
       </c>
       <c r="D88">
-        <v>4200.271865526517</v>
+        <v>4167.681635291248</v>
       </c>
       <c r="E88">
-        <v>10183.31185859061</v>
+        <v>10313.71815440557</v>
       </c>
       <c r="F88">
-        <v>11214.94144008623</v>
+        <v>11345.34773590119</v>
       </c>
       <c r="G88">
         <v>439.4</v>
@@ -8494,37 +8494,37 @@
         <v>92.3</v>
       </c>
       <c r="M88">
-        <v>2644.483191572334</v>
+        <v>2675.232996125501</v>
       </c>
       <c r="N88">
-        <v>-2552.183191572334</v>
+        <v>-2582.932996125501</v>
       </c>
       <c r="O88">
-        <v>-587.0021340616368</v>
+        <v>-594.0745891088652</v>
       </c>
       <c r="P88">
-        <v>-1965.181057510697</v>
+        <v>-1988.858407016636</v>
       </c>
       <c r="Q88">
-        <v>-1933.581057510697</v>
+        <v>-1957.258407016636</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6258172761959581</v>
+        <v>0.6704339897494933</v>
       </c>
       <c r="T88">
-        <v>8.972682795152913</v>
+        <v>9.66288916401083</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.008027655485825888</v>
+        <v>0.007935383583689958</v>
       </c>
       <c r="W88">
-        <v>0.2339070788364423</v>
+        <v>0.2339288365509659</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.03490284993837345</v>
+        <v>0.03450166775517383</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8540,22 +8540,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2906745064667745</v>
+        <v>0.2925745064667745</v>
       </c>
       <c r="C89">
-        <v>-6738.266100609942</v>
+        <v>-6900.760780352513</v>
       </c>
       <c r="D89">
-        <v>4167.681635291248</v>
+        <v>4135.593251363634</v>
       </c>
       <c r="E89">
-        <v>10313.71815440557</v>
+        <v>10444.12445022053</v>
       </c>
       <c r="F89">
-        <v>11345.34773590119</v>
+        <v>11475.75403171615</v>
       </c>
       <c r="G89">
         <v>439.4</v>
@@ -8576,37 +8576,37 @@
         <v>92.3</v>
       </c>
       <c r="M89">
-        <v>2675.232996125501</v>
+        <v>2705.982800678668</v>
       </c>
       <c r="N89">
-        <v>-2582.932996125501</v>
+        <v>-2613.682800678668</v>
       </c>
       <c r="O89">
-        <v>-594.0745891088652</v>
+        <v>-601.1470441560936</v>
       </c>
       <c r="P89">
-        <v>-1988.858407016636</v>
+        <v>-2012.535756522574</v>
       </c>
       <c r="Q89">
-        <v>-1957.258407016636</v>
+        <v>-1980.935756522574</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6704339897494933</v>
+        <v>0.7224868222286177</v>
       </c>
       <c r="T89">
-        <v>9.66288916401083</v>
+        <v>10.4681299276784</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.007935383583689958</v>
+        <v>0.007845208770238934</v>
       </c>
       <c r="W89">
-        <v>0.2339288365509659</v>
+        <v>0.2339500997719777</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.03450166775517383</v>
+        <v>0.03410960334886504</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8622,22 +8622,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2925745064667745</v>
+        <v>0.2944745064667745</v>
       </c>
       <c r="C90">
-        <v>-6900.760780352513</v>
+        <v>-7062.7651168723</v>
       </c>
       <c r="D90">
-        <v>4135.593251363634</v>
+        <v>4103.995210658803</v>
       </c>
       <c r="E90">
-        <v>10444.12445022053</v>
+        <v>10574.53074603548</v>
       </c>
       <c r="F90">
-        <v>11475.75403171615</v>
+        <v>11606.1603275311</v>
       </c>
       <c r="G90">
         <v>439.4</v>
@@ -8658,37 +8658,37 @@
         <v>92.3</v>
       </c>
       <c r="M90">
-        <v>2705.982800678668</v>
+        <v>2736.732605231834</v>
       </c>
       <c r="N90">
-        <v>-2613.682800678668</v>
+        <v>-2644.432605231834</v>
       </c>
       <c r="O90">
-        <v>-601.1470441560936</v>
+        <v>-608.2194992033218</v>
       </c>
       <c r="P90">
-        <v>-2012.535756522574</v>
+        <v>-2036.213106028512</v>
       </c>
       <c r="Q90">
-        <v>-1980.935756522574</v>
+        <v>-2004.613106028512</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7224868222286177</v>
+        <v>0.7840038060675831</v>
       </c>
       <c r="T90">
-        <v>10.4681299276784</v>
+        <v>11.41977810292189</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.007845208770238934</v>
+        <v>0.007757060357090184</v>
       </c>
       <c r="W90">
-        <v>0.2339500997719777</v>
+        <v>0.2339708851677981</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.03410960334886504</v>
+        <v>0.03372634937865304</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8704,22 +8704,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2944745064667745</v>
+        <v>0.2963745064667744</v>
       </c>
       <c r="C91">
-        <v>-7062.7651168723</v>
+        <v>-7224.29026436216</v>
       </c>
       <c r="D91">
-        <v>4103.995210658803</v>
+        <v>4072.8763589839</v>
       </c>
       <c r="E91">
-        <v>10574.53074603548</v>
+        <v>10704.93704185044</v>
       </c>
       <c r="F91">
-        <v>11606.1603275311</v>
+        <v>11736.56662334606</v>
       </c>
       <c r="G91">
         <v>439.4</v>
@@ -8740,37 +8740,37 @@
         <v>92.3</v>
       </c>
       <c r="M91">
-        <v>2736.732605231834</v>
+        <v>2767.482409785001</v>
       </c>
       <c r="N91">
-        <v>-2644.432605231834</v>
+        <v>-2675.182409785001</v>
       </c>
       <c r="O91">
-        <v>-608.2194992033218</v>
+        <v>-615.2919542505502</v>
       </c>
       <c r="P91">
-        <v>-2036.213106028512</v>
+        <v>-2059.890455534451</v>
       </c>
       <c r="Q91">
-        <v>-2004.613106028512</v>
+        <v>-2028.290455534451</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7840038060675831</v>
+        <v>0.8578241866743415</v>
       </c>
       <c r="T91">
-        <v>11.41977810292189</v>
+        <v>12.56175591321408</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.007757060357090184</v>
+        <v>0.007670870797566959</v>
       </c>
       <c r="W91">
-        <v>0.2339708851677981</v>
+        <v>0.2339912086659337</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.03372634937865304</v>
+        <v>0.03335161216333471</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8786,22 +8786,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2963745064667744</v>
+        <v>0.2982745064667744</v>
       </c>
       <c r="C92">
-        <v>-7224.29026436216</v>
+        <v>-7385.347041250887</v>
       </c>
       <c r="D92">
-        <v>4072.8763589839</v>
+        <v>4042.225877910128</v>
       </c>
       <c r="E92">
-        <v>10704.93704185044</v>
+        <v>10835.34333766539</v>
       </c>
       <c r="F92">
-        <v>11736.56662334606</v>
+        <v>11866.97291916101</v>
       </c>
       <c r="G92">
         <v>439.4</v>
@@ -8822,37 +8822,37 @@
         <v>92.3</v>
       </c>
       <c r="M92">
-        <v>2767.482409785001</v>
+        <v>2798.232214338168</v>
       </c>
       <c r="N92">
-        <v>-2675.182409785001</v>
+        <v>-2705.932214338167</v>
       </c>
       <c r="O92">
-        <v>-615.2919542505502</v>
+        <v>-622.3644092977785</v>
       </c>
       <c r="P92">
-        <v>-2059.890455534451</v>
+        <v>-2083.567805040389</v>
       </c>
       <c r="Q92">
-        <v>-2028.290455534451</v>
+        <v>-2051.967805040389</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8578241866743415</v>
+        <v>0.9480490963048239</v>
       </c>
       <c r="T92">
-        <v>12.56175591321408</v>
+        <v>13.95750657023787</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.007670870797566959</v>
+        <v>0.007586575514077212</v>
       </c>
       <c r="W92">
-        <v>0.2339912086659337</v>
+        <v>0.2340110854937806</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.03335161216333471</v>
+        <v>0.0329851109307705</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8868,22 +8868,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2982745064667744</v>
+        <v>0.3001745064667745</v>
       </c>
       <c r="C93">
-        <v>-7385.347041250887</v>
+        <v>-7545.94594274283</v>
       </c>
       <c r="D93">
-        <v>4042.225877910128</v>
+        <v>4012.033272233142</v>
       </c>
       <c r="E93">
-        <v>10835.34333766539</v>
+        <v>10965.74963348035</v>
       </c>
       <c r="F93">
-        <v>11866.97291916101</v>
+        <v>11997.37921497597</v>
       </c>
       <c r="G93">
         <v>439.4</v>
@@ -8904,37 +8904,37 @@
         <v>92.3</v>
       </c>
       <c r="M93">
-        <v>2798.232214338168</v>
+        <v>2828.982018891335</v>
       </c>
       <c r="N93">
-        <v>-2705.932214338167</v>
+        <v>-2736.682018891334</v>
       </c>
       <c r="O93">
-        <v>-622.3644092977785</v>
+        <v>-629.4368643450069</v>
       </c>
       <c r="P93">
-        <v>-2083.567805040389</v>
+        <v>-2107.245154546327</v>
       </c>
       <c r="Q93">
-        <v>-2051.967805040389</v>
+        <v>-2075.645154546327</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9480490963048239</v>
+        <v>1.060830233342927</v>
       </c>
       <c r="T93">
-        <v>13.95750657023787</v>
+        <v>15.70219489151761</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.007586575514077212</v>
+        <v>0.007504112736750285</v>
       </c>
       <c r="W93">
-        <v>0.2340110854937806</v>
+        <v>0.2340305302166743</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.0329851109307705</v>
+        <v>0.03262657711630568</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8950,22 +8950,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3001745064667745</v>
+        <v>0.3020745064667745</v>
       </c>
       <c r="C94">
-        <v>-7545.94594274283</v>
+        <v>-7706.0971527997</v>
       </c>
       <c r="D94">
-        <v>4012.033272233142</v>
+        <v>3982.28835799123</v>
       </c>
       <c r="E94">
-        <v>10965.74963348035</v>
+        <v>11096.15592929531</v>
       </c>
       <c r="F94">
-        <v>11997.37921497597</v>
+        <v>12127.78551079093</v>
       </c>
       <c r="G94">
         <v>439.4</v>
@@ -8986,37 +8986,37 @@
         <v>92.3</v>
       </c>
       <c r="M94">
-        <v>2828.982018891335</v>
+        <v>2859.731823444501</v>
       </c>
       <c r="N94">
-        <v>-2736.682018891334</v>
+        <v>-2767.431823444501</v>
       </c>
       <c r="O94">
-        <v>-629.4368643450069</v>
+        <v>-636.5093193922353</v>
       </c>
       <c r="P94">
-        <v>-2107.245154546327</v>
+        <v>-2130.922504052266</v>
       </c>
       <c r="Q94">
-        <v>-2075.645154546327</v>
+        <v>-2099.322504052266</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.060830233342927</v>
+        <v>1.205834552391917</v>
       </c>
       <c r="T94">
-        <v>15.70219489151761</v>
+        <v>17.94536559030584</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.007504112736750285</v>
+        <v>0.007423423352484153</v>
       </c>
       <c r="W94">
-        <v>0.2340305302166743</v>
+        <v>0.2340495567734842</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.03262657711630568</v>
+        <v>0.03227575370645286</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9032,22 +9032,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3020745064667745</v>
+        <v>0.3039745064667745</v>
       </c>
       <c r="C95">
-        <v>-7706.0971527997</v>
+        <v>-7865.810555593312</v>
       </c>
       <c r="D95">
-        <v>3982.28835799123</v>
+        <v>3952.981251012573</v>
       </c>
       <c r="E95">
-        <v>11096.15592929531</v>
+        <v>11226.56222511026</v>
       </c>
       <c r="F95">
-        <v>12127.78551079093</v>
+        <v>12258.19180660588</v>
       </c>
       <c r="G95">
         <v>439.4</v>
@@ -9068,37 +9068,37 @@
         <v>92.3</v>
       </c>
       <c r="M95">
-        <v>2859.731823444501</v>
+        <v>2890.481627997668</v>
       </c>
       <c r="N95">
-        <v>-2767.431823444501</v>
+        <v>-2798.181627997667</v>
       </c>
       <c r="O95">
-        <v>-636.5093193922353</v>
+        <v>-643.5817744394635</v>
       </c>
       <c r="P95">
-        <v>-2130.922504052266</v>
+        <v>-2154.599853558204</v>
       </c>
       <c r="Q95">
-        <v>-2099.322504052266</v>
+        <v>-2122.999853558204</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.205834552391917</v>
+        <v>1.399173644457237</v>
       </c>
       <c r="T95">
-        <v>17.94536559030584</v>
+        <v>20.93625985535682</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.007423423352484153</v>
+        <v>0.007344450763627939</v>
       </c>
       <c r="W95">
-        <v>0.2340495567734842</v>
+        <v>0.2340681785099366</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.03227575370645286</v>
+        <v>0.0319323946244694</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9114,22 +9114,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3039745064667745</v>
+        <v>0.3058745064667745</v>
       </c>
       <c r="C96">
-        <v>-7865.810555593312</v>
+        <v>-8025.095746456305</v>
       </c>
       <c r="D96">
-        <v>3952.981251012573</v>
+        <v>3924.102355964536</v>
       </c>
       <c r="E96">
-        <v>11226.56222511026</v>
+        <v>11356.96852092522</v>
       </c>
       <c r="F96">
-        <v>12258.19180660588</v>
+        <v>12388.59810242084</v>
       </c>
       <c r="G96">
         <v>439.4</v>
@@ -9150,37 +9150,37 @@
         <v>92.3</v>
       </c>
       <c r="M96">
-        <v>2890.481627997668</v>
+        <v>2921.231432550835</v>
       </c>
       <c r="N96">
-        <v>-2798.181627997667</v>
+        <v>-2828.931432550834</v>
       </c>
       <c r="O96">
-        <v>-643.5817744394635</v>
+        <v>-650.654229486692</v>
       </c>
       <c r="P96">
-        <v>-2154.599853558204</v>
+        <v>-2178.277203064143</v>
       </c>
       <c r="Q96">
-        <v>-2122.999853558204</v>
+        <v>-2146.677203064143</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.399173644457237</v>
+        <v>1.669848373348685</v>
       </c>
       <c r="T96">
-        <v>20.93625985535682</v>
+        <v>25.12351182642819</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.007344450763627939</v>
+        <v>0.00726714075558975</v>
       </c>
       <c r="W96">
-        <v>0.2340681785099366</v>
+        <v>0.234086408209832</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.0319323946244694</v>
+        <v>0.03159626415473815</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9196,22 +9196,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3058745064667745</v>
+        <v>0.3077745064667745</v>
       </c>
       <c r="C97">
-        <v>-8025.095746456305</v>
+        <v>-8183.962042356337</v>
       </c>
       <c r="D97">
-        <v>3924.102355964536</v>
+        <v>3895.642355879459</v>
       </c>
       <c r="E97">
-        <v>11356.96852092522</v>
+        <v>11487.37481674018</v>
       </c>
       <c r="F97">
-        <v>12388.59810242084</v>
+        <v>12519.0043982358</v>
       </c>
       <c r="G97">
         <v>439.4</v>
@@ -9232,37 +9232,37 @@
         <v>92.3</v>
       </c>
       <c r="M97">
-        <v>2921.231432550835</v>
+        <v>2951.981237104001</v>
       </c>
       <c r="N97">
-        <v>-2828.931432550834</v>
+        <v>-2859.681237104001</v>
       </c>
       <c r="O97">
-        <v>-650.654229486692</v>
+        <v>-657.7266845339202</v>
       </c>
       <c r="P97">
-        <v>-2178.277203064143</v>
+        <v>-2201.954552570081</v>
       </c>
       <c r="Q97">
-        <v>-2146.677203064143</v>
+        <v>-2170.354552570081</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.669848373348685</v>
+        <v>2.075860466685857</v>
       </c>
       <c r="T97">
-        <v>25.12351182642819</v>
+        <v>31.40438978303526</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.00726714075558975</v>
+        <v>0.007191441372719023</v>
       </c>
       <c r="W97">
-        <v>0.234086408209832</v>
+        <v>0.2341042581243129</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.03159626415473815</v>
+        <v>0.03126713640312628</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9278,22 +9278,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3077745064667745</v>
+        <v>0.3096745064667745</v>
       </c>
       <c r="C98">
-        <v>-8183.962042356337</v>
+        <v>-8342.418491917779</v>
       </c>
       <c r="D98">
-        <v>3895.642355879459</v>
+        <v>3867.592202132974</v>
       </c>
       <c r="E98">
-        <v>11487.37481674018</v>
+        <v>11617.78111255513</v>
       </c>
       <c r="F98">
-        <v>12519.0043982358</v>
+        <v>12649.41069405075</v>
       </c>
       <c r="G98">
         <v>439.4</v>
@@ -9314,37 +9314,37 @@
         <v>92.3</v>
       </c>
       <c r="M98">
-        <v>2951.981237104001</v>
+        <v>2982.731041657167</v>
       </c>
       <c r="N98">
-        <v>-2859.681237104001</v>
+        <v>-2890.431041657167</v>
       </c>
       <c r="O98">
-        <v>-657.7266845339202</v>
+        <v>-664.7991395811484</v>
       </c>
       <c r="P98">
-        <v>-2201.954552570081</v>
+        <v>-2225.631902076018</v>
       </c>
       <c r="Q98">
-        <v>-2170.354552570081</v>
+        <v>-2194.031902076018</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.075860466685852</v>
+        <v>2.752547288914469</v>
       </c>
       <c r="T98">
-        <v>31.40438978303517</v>
+        <v>41.87251971071356</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.007191441372719023</v>
+        <v>0.007117302801866252</v>
       </c>
       <c r="W98">
-        <v>0.2341042581243129</v>
+        <v>0.2341217399993199</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.03126713640312628</v>
+        <v>0.03094479479072287</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9360,22 +9360,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3096745064667745</v>
+        <v>0.3115745064667745</v>
       </c>
       <c r="C99">
-        <v>-8342.418491917779</v>
+        <v>-8500.473885013522</v>
       </c>
       <c r="D99">
-        <v>3867.592202132974</v>
+        <v>3839.943104852187</v>
       </c>
       <c r="E99">
-        <v>11617.78111255513</v>
+        <v>11748.18740837009</v>
       </c>
       <c r="F99">
-        <v>12649.41069405075</v>
+        <v>12779.81698986571</v>
       </c>
       <c r="G99">
         <v>439.4</v>
@@ -9396,37 +9396,37 @@
         <v>92.3</v>
       </c>
       <c r="M99">
-        <v>2982.731041657167</v>
+        <v>3013.480846210334</v>
       </c>
       <c r="N99">
-        <v>-2890.431041657167</v>
+        <v>-2921.180846210334</v>
       </c>
       <c r="O99">
-        <v>-664.7991395811484</v>
+        <v>-671.8715946283769</v>
       </c>
       <c r="P99">
-        <v>-2225.631902076018</v>
+        <v>-2249.309251581957</v>
       </c>
       <c r="Q99">
-        <v>-2194.031902076018</v>
+        <v>-2217.709251581957</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.752547288914469</v>
+        <v>4.105920933371704</v>
       </c>
       <c r="T99">
-        <v>41.87251971071356</v>
+        <v>62.80877956607034</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.007117302801866252</v>
+        <v>0.007044677263071697</v>
       </c>
       <c r="W99">
-        <v>0.2341217399993199</v>
+        <v>0.2341388651013677</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.03094479479072287</v>
+        <v>0.03062903157857266</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9442,22 +9442,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3115745064667745</v>
+        <v>0.3134745064667745</v>
       </c>
       <c r="C100">
-        <v>-8500.473885013522</v>
+        <v>-8658.136761948295</v>
       </c>
       <c r="D100">
-        <v>3839.943104852187</v>
+        <v>3812.686523732368</v>
       </c>
       <c r="E100">
-        <v>11748.18740837009</v>
+        <v>11878.59370418504</v>
       </c>
       <c r="F100">
-        <v>12779.81698986571</v>
+        <v>12910.22328568066</v>
       </c>
       <c r="G100">
         <v>439.4</v>
@@ -9478,37 +9478,37 @@
         <v>92.3</v>
       </c>
       <c r="M100">
-        <v>3013.480846210334</v>
+        <v>3044.230650763501</v>
       </c>
       <c r="N100">
-        <v>-2921.180846210334</v>
+        <v>-2951.930650763501</v>
       </c>
       <c r="O100">
-        <v>-671.8715946283769</v>
+        <v>-678.9440496756051</v>
       </c>
       <c r="P100">
-        <v>-2249.309251581957</v>
+        <v>-2272.986601087895</v>
       </c>
       <c r="Q100">
-        <v>-2217.709251581957</v>
+        <v>-2241.386601087896</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.105920933371704</v>
+        <v>8.166041866743408</v>
       </c>
       <c r="T100">
-        <v>62.80877956607034</v>
+        <v>125.6175591321407</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.007044677263071697</v>
+        <v>0.006973518906879054</v>
       </c>
       <c r="W100">
-        <v>0.2341388651013677</v>
+        <v>0.2341556442417579</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9516,91 +9516,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.03062903157857266</v>
+        <v>0.03031964742121329</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3134745064667745</v>
-      </c>
-      <c r="C101">
-        <v>-8658.136761948295</v>
-      </c>
-      <c r="D101">
-        <v>3812.686523732368</v>
-      </c>
-      <c r="E101">
-        <v>11878.59370418504</v>
-      </c>
-      <c r="F101">
-        <v>12910.22328568066</v>
-      </c>
-      <c r="G101">
-        <v>439.4</v>
-      </c>
-      <c r="H101">
-        <v>12009</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>123.9</v>
-      </c>
-      <c r="K101">
-        <v>31.60000000000001</v>
-      </c>
-      <c r="L101">
-        <v>92.3</v>
-      </c>
-      <c r="M101">
-        <v>3044.230650763501</v>
-      </c>
-      <c r="N101">
-        <v>-2951.930650763501</v>
-      </c>
-      <c r="O101">
-        <v>-678.9440496756051</v>
-      </c>
-      <c r="P101">
-        <v>-2272.986601087895</v>
-      </c>
-      <c r="Q101">
-        <v>-2241.386601087896</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.166041866743408</v>
-      </c>
-      <c r="T101">
-        <v>125.6175591321407</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.006973518906879054</v>
-      </c>
-      <c r="W101">
-        <v>0.2341556442417579</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.03031964742121329</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
